--- a/Новая форма (Ответы).xlsx
+++ b/Новая форма (Ответы).xlsx
@@ -1,29 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinalien/Documents/guap_study/4_semester/statistical_processing /SOI-lr3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinalien/Documents/guap_study/4_semester/statistical_processing /SOI-lr3/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318454FE-EC24-FD42-B4D5-F03D9A7B696D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30BB539-C3AF-1041-8F30-09B46692CF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ответы на форму (1)" sheetId="1" r:id="rId1"/>
     <sheet name="Фактор 1 - качество" sheetId="2" r:id="rId2"/>
     <sheet name="Фактор 2 - время" sheetId="3" r:id="rId3"/>
     <sheet name="Фактор 3 - стоимость (экономия)" sheetId="4" r:id="rId4"/>
+    <sheet name="OLS Регрессия" sheetId="18" r:id="rId5"/>
+    <sheet name="Описательная статистика" sheetId="17" r:id="rId6"/>
+    <sheet name="Матрица оценок" sheetId="16" r:id="rId7"/>
+    <sheet name="Матрица нагрузок" sheetId="15" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="169">
   <si>
     <t>Отметка времени</t>
   </si>
@@ -366,15 +383,182 @@
   <si>
     <t xml:space="preserve">Цена блюд соответствуют их качеству </t>
   </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Дисперсия</t>
+  </si>
+  <si>
+    <t>Мода</t>
+  </si>
+  <si>
+    <t>Медиана</t>
+  </si>
+  <si>
+    <t>Среднее арифметическое</t>
+  </si>
+  <si>
+    <t>Вопросы</t>
+  </si>
+  <si>
+    <t>Предиктор</t>
+  </si>
+  <si>
+    <t>Коэф. β</t>
+  </si>
+  <si>
+    <t>Ст. ошибка</t>
+  </si>
+  <si>
+    <t>t-статистика</t>
+  </si>
+  <si>
+    <t>p-значение</t>
+  </si>
+  <si>
+    <t>β₀ (константа)</t>
+  </si>
+  <si>
+    <t>Экономия</t>
+  </si>
+  <si>
+    <t>Время</t>
+  </si>
+  <si>
+    <t>Качество</t>
+  </si>
+  <si>
+    <t>q11 — Акции / программы</t>
+  </si>
+  <si>
+    <t>q10 — Выгодные цены</t>
+  </si>
+  <si>
+    <t>q9 — Порции = цена</t>
+  </si>
+  <si>
+    <t>q8 — Цена = качество</t>
+  </si>
+  <si>
+    <t>q7 — Расстояние невелико</t>
+  </si>
+  <si>
+    <t>q6 — Быстрое обслуживание</t>
+  </si>
+  <si>
+    <t>q5 — Ожидание ≤15 мин</t>
+  </si>
+  <si>
+    <t>q4 — Чистота в зале</t>
+  </si>
+  <si>
+    <t>q3 — Сытость до конца дня</t>
+  </si>
+  <si>
+    <t>q2 — Свежесть продуктов</t>
+  </si>
+  <si>
+    <t>q1 — Размер порций</t>
+  </si>
+  <si>
+    <t>Экономия (F3)</t>
+  </si>
+  <si>
+    <t>Время (F2)</t>
+  </si>
+  <si>
+    <t>Качество (F1)</t>
+  </si>
+  <si>
+    <t>Критерий</t>
+  </si>
+  <si>
+    <t>Условное число</t>
+  </si>
+  <si>
+    <t>Prob(JB)</t>
+  </si>
+  <si>
+    <t>Jarque-Bera (JB)</t>
+  </si>
+  <si>
+    <t>Durbin-Watson</t>
+  </si>
+  <si>
+    <t>Prob(Omnibus)</t>
+  </si>
+  <si>
+    <t>Omnibus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Диагностика модели</t>
+  </si>
+  <si>
+    <t>β₃ Фактор_Экономия</t>
+  </si>
+  <si>
+    <t>β₂ Фактор_Время</t>
+  </si>
+  <si>
+    <t>β₁ Фактор_Качество</t>
+  </si>
+  <si>
+    <t>0.975]</t>
+  </si>
+  <si>
+    <t>[0.025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Коэффициенты регрессии</t>
+  </si>
+  <si>
+    <t>BIC</t>
+  </si>
+  <si>
+    <t>AIC</t>
+  </si>
+  <si>
+    <t>p-value (F-статистика)</t>
+  </si>
+  <si>
+    <t>F-статистика</t>
+  </si>
+  <si>
+    <t>Скорректированный R²</t>
+  </si>
+  <si>
+    <t>R² (коэфф. детерминации)</t>
+  </si>
+  <si>
+    <t>Число предикторов</t>
+  </si>
+  <si>
+    <t>Число наблюдений</t>
+  </si>
+  <si>
+    <t>Наименьшие квадраты (OLS)</t>
+  </si>
+  <si>
+    <t>Метод оценки</t>
+  </si>
+  <si>
+    <t>Зависимая переменная</t>
+  </si>
+  <si>
+    <t>Результаты OLS-регрессии: y = Важность КБЖУ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -385,6 +569,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -401,8 +586,72 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -427,8 +676,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -501,11 +768,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -570,20 +853,119 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{520A7B08-80AD-D749-9D77-DA2D7C543291}"/>
   </cellStyles>
   <dxfs count="90">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -840,20 +1222,13 @@
       <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -879,13 +1254,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF5B3F86"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF5B3F86"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF5B3F86"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF5B3F86"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Ответы на форму (1)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="86"/>
-      <tableStyleElement type="headerRow" dxfId="89"/>
-      <tableStyleElement type="firstRowStripe" dxfId="88"/>
-      <tableStyleElement type="secondRowStripe" dxfId="87"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="89"/>
+      <tableStyleElement type="headerRow" dxfId="88"/>
+      <tableStyleElement type="firstRowStripe" dxfId="87"/>
+      <tableStyleElement type="secondRowStripe" dxfId="86"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -904,91 +1295,91 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:CE32" headerRowDxfId="0" dataDxfId="1" totalsRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:CE32" headerRowDxfId="85" dataDxfId="84" totalsRowDxfId="83">
   <tableColumns count="83">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Отметка времени" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Ваш пол:" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Ваш средний бюджет на 1 обед:" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Насколько для вас важен состав еды по КБЖУ?" dataDxfId="82"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Насколько вы привередливы к еде?" dataDxfId="81"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Как часто вы едите вне дома в учебное время?" dataDxfId="80"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Порции в этом заведении достаточно большие, чтобы наесться [Усы лисы]" dataDxfId="79"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Порции в этом заведении достаточно большие, чтобы наесться [Столовая на БМ]" dataDxfId="78"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Порции в этом заведении достаточно большие, чтобы наесться [Теремок]" dataDxfId="77"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Порции в этом заведении достаточно большие, чтобы наесться [Евразия]" dataDxfId="76"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Порции в этом заведении достаточно большие, чтобы наесться [Burger King в ТЦ Сенная]" dataDxfId="75"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Порции в этом заведении достаточно большие, чтобы наесться [Rostic's в ТЦ Сенная]" dataDxfId="74"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Порции в этом заведении достаточно большие, чтобы наесться [Вкусно - и точка в ПИКе]" dataDxfId="73"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="У меня есть уверенность в свежести и безопасности продуктов в этом месте [Усы лисы]" dataDxfId="72"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="У меня есть уверенность в свежести и безопасности продуктов в этом месте [Столовая на БМ]" dataDxfId="71"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="У меня есть уверенность в свежести и безопасности продуктов в этом месте [Теремок]" dataDxfId="70"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="У меня есть уверенность в свежести и безопасности продуктов в этом месте [Евразия]" dataDxfId="69"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="У меня есть уверенность в свежести и безопасности продуктов в этом месте [Burger King в ТЦ Сенная]" dataDxfId="68"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="У меня есть уверенность в свежести и безопасности продуктов в этом месте [Rostic's в ТЦ Сенная]" dataDxfId="67"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="У меня есть уверенность в свежести и безопасности продуктов в этом месте [Вкусно - и точка в ПИКе]" dataDxfId="66"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="После обеда здесь чувство сытости сохраняется до конца учебного дня [Усы лисы]" dataDxfId="65"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="После обеда здесь чувство сытости сохраняется до конца учебного дня [Столовая на БМ]" dataDxfId="64"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="После обеда здесь чувство сытости сохраняется до конца учебного дня [Теремок]" dataDxfId="63"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="После обеда здесь чувство сытости сохраняется до конца учебного дня [Евразия]" dataDxfId="62"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="После обеда здесь чувство сытости сохраняется до конца учебного дня [Burger King в ТЦ Сенная]" dataDxfId="61"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="После обеда здесь чувство сытости сохраняется до конца учебного дня [Rostic's в ТЦ Сенная]" dataDxfId="60"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="После обеда здесь чувство сытости сохраняется до конца учебного дня [Вкусно - и точка в ПИКе]" dataDxfId="59"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="В зале чистота и порядок [Усы лисы]" dataDxfId="58"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="В зале чистота и порядок [Столовая на БМ]" dataDxfId="57"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="В зале чистота и порядок [Теремок]" dataDxfId="56"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="В зале чистота и порядок [Евразия]" dataDxfId="55"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="В зале чистота и порядок [Burger King в ТЦ Сенная]" dataDxfId="54"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="В зале чистота и порядок [Rostic's в ТЦ Сенная]" dataDxfId="53"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="В зале чистота и порядок [Вкусно - и точка в ПИКе]" dataDxfId="52"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Время ожидания заказа обычно не превышает 10-15 минут [Усы лисы]" dataDxfId="51"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Время ожидания заказа обычно не превышает 10-15 минут [Столовая на БМ]" dataDxfId="50"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Время ожидания заказа обычно не превышает 10-15 минут [Теремок]" dataDxfId="49"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Время ожидания заказа обычно не превышает 10-15 минут [Евразия]" dataDxfId="48"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Время ожидания заказа обычно не превышает 10-15 минут [Burger King в ТЦ Сенная]" dataDxfId="47"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Время ожидания заказа обычно не превышает 10-15 минут [Rostic's в ТЦ Сенная]" dataDxfId="46"/>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Время ожидания заказа обычно не превышает 10-15 минут [Вкусно - и точка в ПИКе]" dataDxfId="45"/>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="В этом заведении всегда быстрое обслуживание, даже в час-пик [Усы лисы]" dataDxfId="44"/>
-    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="В этом заведении всегда быстрое обслуживание, даже в час-пик [Столовая на БМ]" dataDxfId="43"/>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="В этом заведении всегда быстрое обслуживание, даже в час-пик [Теремок]" dataDxfId="42"/>
-    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="В этом заведении всегда быстрое обслуживание, даже в час-пик [Евразия]" dataDxfId="41"/>
-    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="В этом заведении всегда быстрое обслуживание, даже в час-пик [Burger King в ТЦ Сенная]" dataDxfId="40"/>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="В этом заведении всегда быстрое обслуживание, даже в час-пик [Rostic's в ТЦ Сенная]" dataDxfId="39"/>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="В этом заведении всегда быстрое обслуживание, даже в час-пик [Вкусно - и точка в ПИКе]" dataDxfId="38"/>
-    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="Путь до заведения не занимает много времени [Усы лисы]" dataDxfId="37"/>
-    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="Путь до заведения не занимает много времени [Столовая на БМ]" dataDxfId="36"/>
-    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Путь до заведения не занимает много времени [Теремок]" dataDxfId="35"/>
-    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Путь до заведения не занимает много времени [Евразия]" dataDxfId="34"/>
-    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="Путь до заведения не занимает много времени [Burger King в ТЦ Сенная]" dataDxfId="33"/>
-    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="Путь до заведения не занимает много времени [Rostic's в ТЦ Сенная]" dataDxfId="32"/>
-    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Путь до заведения не занимает много времени [Вкусно - и точка в ПИКе]" dataDxfId="31"/>
-    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Цена блюд соответствуют их качеству [Усы лисы]" dataDxfId="30"/>
-    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Цена блюд соответствуют их качеству [Столовая на БМ]" dataDxfId="29"/>
-    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Цена блюд соответствуют их качеству [Теремок]" dataDxfId="28"/>
-    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Цена блюд соответствуют их качеству [Евразия]" dataDxfId="27"/>
-    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Цена блюд соответствуют их качеству [Burger King в ТЦ Сенная]" dataDxfId="26"/>
-    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Цена блюд соответствуют их качеству [Rostic's в ТЦ Сенная]" dataDxfId="25"/>
-    <tableColumn id="62" xr3:uid="{00000000-0010-0000-0000-00003E000000}" name="Цена блюд соответствуют их качеству [Вкусно - и точка в ПИКе]" dataDxfId="24"/>
-    <tableColumn id="63" xr3:uid="{00000000-0010-0000-0000-00003F000000}" name="Порции в заведении соответствуют цене [Усы лисы]" dataDxfId="23"/>
-    <tableColumn id="64" xr3:uid="{00000000-0010-0000-0000-000040000000}" name="Порции в заведении соответствуют цене [Столовая на БМ]" dataDxfId="22"/>
-    <tableColumn id="65" xr3:uid="{00000000-0010-0000-0000-000041000000}" name="Порции в заведении соответствуют цене [Теремок]" dataDxfId="21"/>
-    <tableColumn id="66" xr3:uid="{00000000-0010-0000-0000-000042000000}" name="Порции в заведении соответствуют цене [Евразия]" dataDxfId="20"/>
-    <tableColumn id="67" xr3:uid="{00000000-0010-0000-0000-000043000000}" name="Порции в заведении соответствуют цене [Burger King в ТЦ Сенная]" dataDxfId="19"/>
-    <tableColumn id="68" xr3:uid="{00000000-0010-0000-0000-000044000000}" name="Порции в заведении соответствуют цене [Rostic's в ТЦ Сенная]" dataDxfId="18"/>
-    <tableColumn id="69" xr3:uid="{00000000-0010-0000-0000-000045000000}" name="Порции в заведении соответствуют цене [Вкусно - и точка в ПИКе]" dataDxfId="17"/>
-    <tableColumn id="70" xr3:uid="{00000000-0010-0000-0000-000046000000}" name="В заведении выгодные цены [Усы лисы]" dataDxfId="16"/>
-    <tableColumn id="71" xr3:uid="{00000000-0010-0000-0000-000047000000}" name="В заведении выгодные цены [Столовая на БМ]" dataDxfId="15"/>
-    <tableColumn id="72" xr3:uid="{00000000-0010-0000-0000-000048000000}" name="В заведении выгодные цены [Теремок]" dataDxfId="14"/>
-    <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="В заведении выгодные цены [Евразия]" dataDxfId="13"/>
-    <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="В заведении выгодные цены [Burger King в ТЦ Сенная]" dataDxfId="12"/>
-    <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="В заведении выгодные цены [Rostic's в ТЦ Сенная]" dataDxfId="11"/>
-    <tableColumn id="76" xr3:uid="{00000000-0010-0000-0000-00004C000000}" name="В заведении выгодные цены [Вкусно - и точка в ПИКе]" dataDxfId="10"/>
-    <tableColumn id="77" xr3:uid="{00000000-0010-0000-0000-00004D000000}" name="В заведении есть различные акции: комбо, ланчи, программа лояльности и пр. [Усы лисы]" dataDxfId="9"/>
-    <tableColumn id="78" xr3:uid="{00000000-0010-0000-0000-00004E000000}" name="В заведении есть различные акции: комбо, ланчи, программа лояльности и пр. [Столовая на БМ]" dataDxfId="8"/>
-    <tableColumn id="79" xr3:uid="{00000000-0010-0000-0000-00004F000000}" name="В заведении есть различные акции: комбо, ланчи, программа лояльности и пр. [Теремок]" dataDxfId="7"/>
-    <tableColumn id="80" xr3:uid="{00000000-0010-0000-0000-000050000000}" name="В заведении есть различные акции: комбо, ланчи, программа лояльности и пр. [Евразия]" dataDxfId="6"/>
-    <tableColumn id="81" xr3:uid="{00000000-0010-0000-0000-000051000000}" name="В заведении есть различные акции: комбо, ланчи, программа лояльности и пр. [Burger King в ТЦ Сенная]" dataDxfId="5"/>
-    <tableColumn id="82" xr3:uid="{00000000-0010-0000-0000-000052000000}" name="В заведении есть различные акции: комбо, ланчи, программа лояльности и пр. [Rostic's в ТЦ Сенная]" dataDxfId="4"/>
-    <tableColumn id="83" xr3:uid="{00000000-0010-0000-0000-000053000000}" name="В заведении есть различные акции: комбо, ланчи, программа лояльности и пр. [Вкусно - и точка в ПИКе]" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Отметка времени" dataDxfId="82"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Ваш пол:" dataDxfId="81"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Ваш средний бюджет на 1 обед:" dataDxfId="80"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Насколько для вас важен состав еды по КБЖУ?" dataDxfId="79"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Насколько вы привередливы к еде?" dataDxfId="78"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Как часто вы едите вне дома в учебное время?" dataDxfId="77"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Порции в этом заведении достаточно большие, чтобы наесться [Усы лисы]" dataDxfId="76"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Порции в этом заведении достаточно большие, чтобы наесться [Столовая на БМ]" dataDxfId="75"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Порции в этом заведении достаточно большие, чтобы наесться [Теремок]" dataDxfId="74"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Порции в этом заведении достаточно большие, чтобы наесться [Евразия]" dataDxfId="73"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Порции в этом заведении достаточно большие, чтобы наесться [Burger King в ТЦ Сенная]" dataDxfId="72"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Порции в этом заведении достаточно большие, чтобы наесться [Rostic's в ТЦ Сенная]" dataDxfId="71"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Порции в этом заведении достаточно большие, чтобы наесться [Вкусно - и точка в ПИКе]" dataDxfId="70"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="У меня есть уверенность в свежести и безопасности продуктов в этом месте [Усы лисы]" dataDxfId="69"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="У меня есть уверенность в свежести и безопасности продуктов в этом месте [Столовая на БМ]" dataDxfId="68"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="У меня есть уверенность в свежести и безопасности продуктов в этом месте [Теремок]" dataDxfId="67"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="У меня есть уверенность в свежести и безопасности продуктов в этом месте [Евразия]" dataDxfId="66"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="У меня есть уверенность в свежести и безопасности продуктов в этом месте [Burger King в ТЦ Сенная]" dataDxfId="65"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="У меня есть уверенность в свежести и безопасности продуктов в этом месте [Rostic's в ТЦ Сенная]" dataDxfId="64"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="У меня есть уверенность в свежести и безопасности продуктов в этом месте [Вкусно - и точка в ПИКе]" dataDxfId="63"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="После обеда здесь чувство сытости сохраняется до конца учебного дня [Усы лисы]" dataDxfId="62"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="После обеда здесь чувство сытости сохраняется до конца учебного дня [Столовая на БМ]" dataDxfId="61"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="После обеда здесь чувство сытости сохраняется до конца учебного дня [Теремок]" dataDxfId="60"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="После обеда здесь чувство сытости сохраняется до конца учебного дня [Евразия]" dataDxfId="59"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="После обеда здесь чувство сытости сохраняется до конца учебного дня [Burger King в ТЦ Сенная]" dataDxfId="58"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="После обеда здесь чувство сытости сохраняется до конца учебного дня [Rostic's в ТЦ Сенная]" dataDxfId="57"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="После обеда здесь чувство сытости сохраняется до конца учебного дня [Вкусно - и точка в ПИКе]" dataDxfId="56"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="В зале чистота и порядок [Усы лисы]" dataDxfId="55"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="В зале чистота и порядок [Столовая на БМ]" dataDxfId="54"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="В зале чистота и порядок [Теремок]" dataDxfId="53"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="В зале чистота и порядок [Евразия]" dataDxfId="52"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="В зале чистота и порядок [Burger King в ТЦ Сенная]" dataDxfId="51"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="В зале чистота и порядок [Rostic's в ТЦ Сенная]" dataDxfId="50"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="В зале чистота и порядок [Вкусно - и точка в ПИКе]" dataDxfId="49"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Время ожидания заказа обычно не превышает 10-15 минут [Усы лисы]" dataDxfId="48"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Время ожидания заказа обычно не превышает 10-15 минут [Столовая на БМ]" dataDxfId="47"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Время ожидания заказа обычно не превышает 10-15 минут [Теремок]" dataDxfId="46"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Время ожидания заказа обычно не превышает 10-15 минут [Евразия]" dataDxfId="45"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Время ожидания заказа обычно не превышает 10-15 минут [Burger King в ТЦ Сенная]" dataDxfId="44"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Время ожидания заказа обычно не превышает 10-15 минут [Rostic's в ТЦ Сенная]" dataDxfId="43"/>
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Время ожидания заказа обычно не превышает 10-15 минут [Вкусно - и точка в ПИКе]" dataDxfId="42"/>
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="В этом заведении всегда быстрое обслуживание, даже в час-пик [Усы лисы]" dataDxfId="41"/>
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="В этом заведении всегда быстрое обслуживание, даже в час-пик [Столовая на БМ]" dataDxfId="40"/>
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="В этом заведении всегда быстрое обслуживание, даже в час-пик [Теремок]" dataDxfId="39"/>
+    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="В этом заведении всегда быстрое обслуживание, даже в час-пик [Евразия]" dataDxfId="38"/>
+    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="В этом заведении всегда быстрое обслуживание, даже в час-пик [Burger King в ТЦ Сенная]" dataDxfId="37"/>
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="В этом заведении всегда быстрое обслуживание, даже в час-пик [Rostic's в ТЦ Сенная]" dataDxfId="36"/>
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="В этом заведении всегда быстрое обслуживание, даже в час-пик [Вкусно - и точка в ПИКе]" dataDxfId="35"/>
+    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="Путь до заведения не занимает много времени [Усы лисы]" dataDxfId="34"/>
+    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="Путь до заведения не занимает много времени [Столовая на БМ]" dataDxfId="33"/>
+    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Путь до заведения не занимает много времени [Теремок]" dataDxfId="32"/>
+    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Путь до заведения не занимает много времени [Евразия]" dataDxfId="31"/>
+    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="Путь до заведения не занимает много времени [Burger King в ТЦ Сенная]" dataDxfId="30"/>
+    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="Путь до заведения не занимает много времени [Rostic's в ТЦ Сенная]" dataDxfId="29"/>
+    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Путь до заведения не занимает много времени [Вкусно - и точка в ПИКе]" dataDxfId="28"/>
+    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Цена блюд соответствуют их качеству [Усы лисы]" dataDxfId="27"/>
+    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Цена блюд соответствуют их качеству [Столовая на БМ]" dataDxfId="26"/>
+    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Цена блюд соответствуют их качеству [Теремок]" dataDxfId="25"/>
+    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Цена блюд соответствуют их качеству [Евразия]" dataDxfId="24"/>
+    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Цена блюд соответствуют их качеству [Burger King в ТЦ Сенная]" dataDxfId="23"/>
+    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Цена блюд соответствуют их качеству [Rostic's в ТЦ Сенная]" dataDxfId="22"/>
+    <tableColumn id="62" xr3:uid="{00000000-0010-0000-0000-00003E000000}" name="Цена блюд соответствуют их качеству [Вкусно - и точка в ПИКе]" dataDxfId="21"/>
+    <tableColumn id="63" xr3:uid="{00000000-0010-0000-0000-00003F000000}" name="Порции в заведении соответствуют цене [Усы лисы]" dataDxfId="20"/>
+    <tableColumn id="64" xr3:uid="{00000000-0010-0000-0000-000040000000}" name="Порции в заведении соответствуют цене [Столовая на БМ]" dataDxfId="19"/>
+    <tableColumn id="65" xr3:uid="{00000000-0010-0000-0000-000041000000}" name="Порции в заведении соответствуют цене [Теремок]" dataDxfId="18"/>
+    <tableColumn id="66" xr3:uid="{00000000-0010-0000-0000-000042000000}" name="Порции в заведении соответствуют цене [Евразия]" dataDxfId="17"/>
+    <tableColumn id="67" xr3:uid="{00000000-0010-0000-0000-000043000000}" name="Порции в заведении соответствуют цене [Burger King в ТЦ Сенная]" dataDxfId="16"/>
+    <tableColumn id="68" xr3:uid="{00000000-0010-0000-0000-000044000000}" name="Порции в заведении соответствуют цене [Rostic's в ТЦ Сенная]" dataDxfId="15"/>
+    <tableColumn id="69" xr3:uid="{00000000-0010-0000-0000-000045000000}" name="Порции в заведении соответствуют цене [Вкусно - и точка в ПИКе]" dataDxfId="14"/>
+    <tableColumn id="70" xr3:uid="{00000000-0010-0000-0000-000046000000}" name="В заведении выгодные цены [Усы лисы]" dataDxfId="13"/>
+    <tableColumn id="71" xr3:uid="{00000000-0010-0000-0000-000047000000}" name="В заведении выгодные цены [Столовая на БМ]" dataDxfId="12"/>
+    <tableColumn id="72" xr3:uid="{00000000-0010-0000-0000-000048000000}" name="В заведении выгодные цены [Теремок]" dataDxfId="11"/>
+    <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="В заведении выгодные цены [Евразия]" dataDxfId="10"/>
+    <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="В заведении выгодные цены [Burger King в ТЦ Сенная]" dataDxfId="9"/>
+    <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="В заведении выгодные цены [Rostic's в ТЦ Сенная]" dataDxfId="8"/>
+    <tableColumn id="76" xr3:uid="{00000000-0010-0000-0000-00004C000000}" name="В заведении выгодные цены [Вкусно - и точка в ПИКе]" dataDxfId="7"/>
+    <tableColumn id="77" xr3:uid="{00000000-0010-0000-0000-00004D000000}" name="В заведении есть различные акции: комбо, ланчи, программа лояльности и пр. [Усы лисы]" dataDxfId="6"/>
+    <tableColumn id="78" xr3:uid="{00000000-0010-0000-0000-00004E000000}" name="В заведении есть различные акции: комбо, ланчи, программа лояльности и пр. [Столовая на БМ]" dataDxfId="5"/>
+    <tableColumn id="79" xr3:uid="{00000000-0010-0000-0000-00004F000000}" name="В заведении есть различные акции: комбо, ланчи, программа лояльности и пр. [Теремок]" dataDxfId="4"/>
+    <tableColumn id="80" xr3:uid="{00000000-0010-0000-0000-000050000000}" name="В заведении есть различные акции: комбо, ланчи, программа лояльности и пр. [Евразия]" dataDxfId="3"/>
+    <tableColumn id="81" xr3:uid="{00000000-0010-0000-0000-000051000000}" name="В заведении есть различные акции: комбо, ланчи, программа лояльности и пр. [Burger King в ТЦ Сенная]" dataDxfId="2"/>
+    <tableColumn id="82" xr3:uid="{00000000-0010-0000-0000-000052000000}" name="В заведении есть различные акции: комбо, ланчи, программа лояльности и пр. [Rostic's в ТЦ Сенная]" dataDxfId="1"/>
+    <tableColumn id="83" xr3:uid="{00000000-0010-0000-0000-000053000000}" name="В заведении есть различные акции: комбо, ланчи, программа лояльности и пр. [Вкусно - и точка в ПИКе]" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Ответы на форму (1)-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17029,4 +17420,8401 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E5EE13-9C88-E342-96AD-C07EAFCA4726}">
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="23.1640625" style="22" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" style="22" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="22" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="22" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="22" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" style="22" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+    </row>
+    <row r="2" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+    </row>
+    <row r="3" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+    </row>
+    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="51">
+        <v>22</v>
+      </c>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+    </row>
+    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="53" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="51">
+        <v>3</v>
+      </c>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+    </row>
+    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="51">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+    </row>
+    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="51">
+        <v>-0.157</v>
+      </c>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+    </row>
+    <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="53" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" s="51">
+        <v>4.8439999999999997E-2</v>
+      </c>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+    </row>
+    <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="B9" s="51">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+    </row>
+    <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="53" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="51">
+        <v>81.31</v>
+      </c>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+    </row>
+    <row r="11" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="51">
+        <v>85.68</v>
+      </c>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+    </row>
+    <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="49"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+    </row>
+    <row r="13" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+    </row>
+    <row r="14" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" s="55" t="s">
+        <v>155</v>
+      </c>
+      <c r="G14" s="55" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" s="45">
+        <v>2.7984</v>
+      </c>
+      <c r="C15" s="45">
+        <v>2.1389999999999998</v>
+      </c>
+      <c r="D15" s="45">
+        <v>1.3080000000000001</v>
+      </c>
+      <c r="E15" s="45">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="F15" s="45">
+        <v>-1.696</v>
+      </c>
+      <c r="G15" s="45">
+        <v>7.2930000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="54" t="s">
+        <v>153</v>
+      </c>
+      <c r="B16" s="45">
+        <v>0.1837</v>
+      </c>
+      <c r="C16" s="45">
+        <v>1.095</v>
+      </c>
+      <c r="D16" s="45">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="E16" s="45">
+        <v>0.86899999999999999</v>
+      </c>
+      <c r="F16" s="45">
+        <v>-2.117</v>
+      </c>
+      <c r="G16" s="45">
+        <v>2.484</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="54" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" s="45">
+        <v>-0.36940000000000001</v>
+      </c>
+      <c r="C17" s="45">
+        <v>1.024</v>
+      </c>
+      <c r="D17" s="45">
+        <v>-0.36099999999999999</v>
+      </c>
+      <c r="E17" s="45">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="F17" s="45">
+        <v>-2.52</v>
+      </c>
+      <c r="G17" s="45">
+        <v>1.7809999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" s="45">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="C18" s="45">
+        <v>0.83899999999999997</v>
+      </c>
+      <c r="D18" s="45">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="E18" s="45">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="F18" s="45">
+        <v>-1.7250000000000001</v>
+      </c>
+      <c r="G18" s="45">
+        <v>1.7989999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="44"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+    </row>
+    <row r="20" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="B20" s="42"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+    </row>
+    <row r="21" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" s="41">
+        <v>4.0030000000000001</v>
+      </c>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+    </row>
+    <row r="22" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="41">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+    </row>
+    <row r="23" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="B23" s="41">
+        <v>1.627</v>
+      </c>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+    </row>
+    <row r="24" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="41">
+        <v>2.0859999999999999</v>
+      </c>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+    </row>
+    <row r="25" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="B25" s="41">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+    </row>
+    <row r="26" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="41">
+        <v>44.4</v>
+      </c>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+    </row>
+    <row r="27" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="57"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+    </row>
+    <row r="28" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="56"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+    </row>
+    <row r="29" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="23"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2250BB67-294F-A140-B569-7F2AE78253E9}">
+  <dimension ref="A1:E78"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="60" style="22" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.15">
+      <c r="A1" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" s="58" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="58" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="58" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="60">
+        <v>4.3230000000000004</v>
+      </c>
+      <c r="C2" s="60">
+        <v>5</v>
+      </c>
+      <c r="D2" s="60">
+        <v>5</v>
+      </c>
+      <c r="E2" s="60">
+        <v>0.89200000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="60">
+        <v>3.129</v>
+      </c>
+      <c r="C3" s="60">
+        <v>3</v>
+      </c>
+      <c r="D3" s="60">
+        <v>2</v>
+      </c>
+      <c r="E3" s="60">
+        <v>1.849</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="59" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="60">
+        <v>3.161</v>
+      </c>
+      <c r="C4" s="60">
+        <v>3</v>
+      </c>
+      <c r="D4" s="60">
+        <v>3</v>
+      </c>
+      <c r="E4" s="60">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="60">
+        <v>3.161</v>
+      </c>
+      <c r="C5" s="60">
+        <v>3</v>
+      </c>
+      <c r="D5" s="60">
+        <v>3</v>
+      </c>
+      <c r="E5" s="60">
+        <v>1.2729999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A6" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="60">
+        <v>3.355</v>
+      </c>
+      <c r="C6" s="60">
+        <v>3</v>
+      </c>
+      <c r="D6" s="60">
+        <v>3</v>
+      </c>
+      <c r="E6" s="60">
+        <v>1.0369999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A7" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="60">
+        <v>3.161</v>
+      </c>
+      <c r="C7" s="60">
+        <v>3</v>
+      </c>
+      <c r="D7" s="60">
+        <v>3</v>
+      </c>
+      <c r="E7" s="60">
+        <v>1.4059999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A8" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="60">
+        <v>3.484</v>
+      </c>
+      <c r="C8" s="60">
+        <v>4</v>
+      </c>
+      <c r="D8" s="60">
+        <v>4</v>
+      </c>
+      <c r="E8" s="60">
+        <v>1.0580000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A9" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="60">
+        <v>3.548</v>
+      </c>
+      <c r="C9" s="60">
+        <v>4</v>
+      </c>
+      <c r="D9" s="60">
+        <v>4</v>
+      </c>
+      <c r="E9" s="60">
+        <v>1.1890000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A10" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="60">
+        <v>3</v>
+      </c>
+      <c r="C10" s="60">
+        <v>3</v>
+      </c>
+      <c r="D10" s="60">
+        <v>3</v>
+      </c>
+      <c r="E10" s="60">
+        <v>1.4670000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A11" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="60">
+        <v>4.1289999999999996</v>
+      </c>
+      <c r="C11" s="60">
+        <v>4</v>
+      </c>
+      <c r="D11" s="60">
+        <v>4</v>
+      </c>
+      <c r="E11" s="60">
+        <v>0.91600000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A12" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="60">
+        <v>3.871</v>
+      </c>
+      <c r="C12" s="60">
+        <v>4</v>
+      </c>
+      <c r="D12" s="60">
+        <v>4</v>
+      </c>
+      <c r="E12" s="60">
+        <v>1.4490000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A13" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="60">
+        <v>3.355</v>
+      </c>
+      <c r="C13" s="60">
+        <v>3</v>
+      </c>
+      <c r="D13" s="60">
+        <v>4</v>
+      </c>
+      <c r="E13" s="60">
+        <v>1.0369999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A14" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="60">
+        <v>3.258</v>
+      </c>
+      <c r="C14" s="60">
+        <v>3</v>
+      </c>
+      <c r="D14" s="60">
+        <v>4</v>
+      </c>
+      <c r="E14" s="60">
+        <v>1.131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A15" s="59" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="60">
+        <v>3.355</v>
+      </c>
+      <c r="C15" s="60">
+        <v>4</v>
+      </c>
+      <c r="D15" s="60">
+        <v>4</v>
+      </c>
+      <c r="E15" s="60">
+        <v>1.103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A16" s="59" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="60">
+        <v>3.677</v>
+      </c>
+      <c r="C16" s="60">
+        <v>4</v>
+      </c>
+      <c r="D16" s="60">
+        <v>5</v>
+      </c>
+      <c r="E16" s="60">
+        <v>2.0259999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A17" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="60">
+        <v>2.968</v>
+      </c>
+      <c r="C17" s="60">
+        <v>3</v>
+      </c>
+      <c r="D17" s="60">
+        <v>4</v>
+      </c>
+      <c r="E17" s="60">
+        <v>1.966</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="60">
+        <v>3.129</v>
+      </c>
+      <c r="C18" s="60">
+        <v>3</v>
+      </c>
+      <c r="D18" s="60">
+        <v>3</v>
+      </c>
+      <c r="E18" s="60">
+        <v>1.716</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="60">
+        <v>3.129</v>
+      </c>
+      <c r="C19" s="60">
+        <v>3</v>
+      </c>
+      <c r="D19" s="60">
+        <v>3</v>
+      </c>
+      <c r="E19" s="60">
+        <v>1.649</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A20" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="60">
+        <v>3.032</v>
+      </c>
+      <c r="C20" s="60">
+        <v>3</v>
+      </c>
+      <c r="D20" s="60">
+        <v>4</v>
+      </c>
+      <c r="E20" s="60">
+        <v>1.5660000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A21" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="60">
+        <v>3</v>
+      </c>
+      <c r="C21" s="60">
+        <v>3</v>
+      </c>
+      <c r="D21" s="60">
+        <v>4</v>
+      </c>
+      <c r="E21" s="60">
+        <v>1.4670000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A22" s="59" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="60">
+        <v>3.194</v>
+      </c>
+      <c r="C22" s="60">
+        <v>3</v>
+      </c>
+      <c r="D22" s="60">
+        <v>4</v>
+      </c>
+      <c r="E22" s="60">
+        <v>1.5609999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23" s="59" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="60">
+        <v>3</v>
+      </c>
+      <c r="C23" s="60">
+        <v>3</v>
+      </c>
+      <c r="D23" s="60">
+        <v>4</v>
+      </c>
+      <c r="E23" s="60">
+        <v>1.333</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A24" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="60">
+        <v>3.387</v>
+      </c>
+      <c r="C24" s="60">
+        <v>4</v>
+      </c>
+      <c r="D24" s="60">
+        <v>4</v>
+      </c>
+      <c r="E24" s="60">
+        <v>1.4450000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A25" s="59" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="60">
+        <v>4.3230000000000004</v>
+      </c>
+      <c r="C25" s="60">
+        <v>5</v>
+      </c>
+      <c r="D25" s="60">
+        <v>5</v>
+      </c>
+      <c r="E25" s="60">
+        <v>0.89200000000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A26" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="60">
+        <v>4.194</v>
+      </c>
+      <c r="C26" s="60">
+        <v>5</v>
+      </c>
+      <c r="D26" s="60">
+        <v>5</v>
+      </c>
+      <c r="E26" s="60">
+        <v>1.2949999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="60">
+        <v>2.677</v>
+      </c>
+      <c r="C27" s="60">
+        <v>3</v>
+      </c>
+      <c r="D27" s="60">
+        <v>3</v>
+      </c>
+      <c r="E27" s="60">
+        <v>1.159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="60">
+        <v>2.677</v>
+      </c>
+      <c r="C28" s="60">
+        <v>3</v>
+      </c>
+      <c r="D28" s="60">
+        <v>3</v>
+      </c>
+      <c r="E28" s="60">
+        <v>1.159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A29" s="59" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="60">
+        <v>2.774</v>
+      </c>
+      <c r="C29" s="60">
+        <v>3</v>
+      </c>
+      <c r="D29" s="60">
+        <v>3</v>
+      </c>
+      <c r="E29" s="60">
+        <v>1.3140000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A30" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="60">
+        <v>4</v>
+      </c>
+      <c r="C30" s="60">
+        <v>5</v>
+      </c>
+      <c r="D30" s="60">
+        <v>5</v>
+      </c>
+      <c r="E30" s="60">
+        <v>2.0670000000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A31" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="60">
+        <v>4.516</v>
+      </c>
+      <c r="C31" s="60">
+        <v>5</v>
+      </c>
+      <c r="D31" s="60">
+        <v>5</v>
+      </c>
+      <c r="E31" s="60">
+        <v>0.85799999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A32" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="60">
+        <v>3.71</v>
+      </c>
+      <c r="C32" s="60">
+        <v>4</v>
+      </c>
+      <c r="D32" s="60">
+        <v>4</v>
+      </c>
+      <c r="E32" s="60">
+        <v>1.0129999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A33" s="59" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="60">
+        <v>2.968</v>
+      </c>
+      <c r="C33" s="60">
+        <v>3</v>
+      </c>
+      <c r="D33" s="60">
+        <v>3</v>
+      </c>
+      <c r="E33" s="60">
+        <v>1.5660000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A34" s="59" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="60">
+        <v>3.903</v>
+      </c>
+      <c r="C34" s="60">
+        <v>4</v>
+      </c>
+      <c r="D34" s="60">
+        <v>4</v>
+      </c>
+      <c r="E34" s="60">
+        <v>1.024</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A35" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="60">
+        <v>3.645</v>
+      </c>
+      <c r="C35" s="60">
+        <v>4</v>
+      </c>
+      <c r="D35" s="60">
+        <v>4</v>
+      </c>
+      <c r="E35" s="60">
+        <v>1.2370000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A36" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="60">
+        <v>3.613</v>
+      </c>
+      <c r="C36" s="60">
+        <v>4</v>
+      </c>
+      <c r="D36" s="60">
+        <v>4</v>
+      </c>
+      <c r="E36" s="60">
+        <v>1.1779999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A37" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="60">
+        <v>3.871</v>
+      </c>
+      <c r="C37" s="60">
+        <v>4</v>
+      </c>
+      <c r="D37" s="60">
+        <v>5</v>
+      </c>
+      <c r="E37" s="60">
+        <v>1.3160000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A38" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="60">
+        <v>3.677</v>
+      </c>
+      <c r="C38" s="60">
+        <v>4</v>
+      </c>
+      <c r="D38" s="60">
+        <v>4</v>
+      </c>
+      <c r="E38" s="60">
+        <v>1.359</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A39" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="60">
+        <v>3.258</v>
+      </c>
+      <c r="C39" s="60">
+        <v>3</v>
+      </c>
+      <c r="D39" s="60">
+        <v>3</v>
+      </c>
+      <c r="E39" s="60">
+        <v>1.5980000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A40" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="60">
+        <v>2.903</v>
+      </c>
+      <c r="C40" s="60">
+        <v>3</v>
+      </c>
+      <c r="D40" s="60">
+        <v>3</v>
+      </c>
+      <c r="E40" s="60">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A41" s="59" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="60">
+        <v>3.355</v>
+      </c>
+      <c r="C41" s="60">
+        <v>3</v>
+      </c>
+      <c r="D41" s="60">
+        <v>3</v>
+      </c>
+      <c r="E41" s="60">
+        <v>1.7030000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A42" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" s="60">
+        <v>3.161</v>
+      </c>
+      <c r="C42" s="60">
+        <v>3</v>
+      </c>
+      <c r="D42" s="60">
+        <v>3</v>
+      </c>
+      <c r="E42" s="60">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A43" s="59" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" s="60">
+        <v>3.226</v>
+      </c>
+      <c r="C43" s="60">
+        <v>3</v>
+      </c>
+      <c r="D43" s="60">
+        <v>3</v>
+      </c>
+      <c r="E43" s="60">
+        <v>1.647</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A44" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" s="60">
+        <v>2.968</v>
+      </c>
+      <c r="C44" s="60">
+        <v>3</v>
+      </c>
+      <c r="D44" s="60">
+        <v>3</v>
+      </c>
+      <c r="E44" s="60">
+        <v>1.766</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A45" s="59" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="60">
+        <v>3.968</v>
+      </c>
+      <c r="C45" s="60">
+        <v>5</v>
+      </c>
+      <c r="D45" s="60">
+        <v>5</v>
+      </c>
+      <c r="E45" s="60">
+        <v>2.6320000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A46" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" s="60">
+        <v>3.194</v>
+      </c>
+      <c r="C46" s="60">
+        <v>3</v>
+      </c>
+      <c r="D46" s="60">
+        <v>3</v>
+      </c>
+      <c r="E46" s="60">
+        <v>1.4950000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A47" s="59" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="60">
+        <v>2.968</v>
+      </c>
+      <c r="C47" s="60">
+        <v>3</v>
+      </c>
+      <c r="D47" s="60">
+        <v>3</v>
+      </c>
+      <c r="E47" s="60">
+        <v>1.5660000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A48" s="59" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="60">
+        <v>2.839</v>
+      </c>
+      <c r="C48" s="60">
+        <v>3</v>
+      </c>
+      <c r="D48" s="60">
+        <v>3</v>
+      </c>
+      <c r="E48" s="60">
+        <v>1.4730000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A49" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="60">
+        <v>2.839</v>
+      </c>
+      <c r="C49" s="60">
+        <v>3</v>
+      </c>
+      <c r="D49" s="60">
+        <v>3</v>
+      </c>
+      <c r="E49" s="60">
+        <v>1.4730000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A50" s="59" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="60">
+        <v>2.806</v>
+      </c>
+      <c r="C50" s="60">
+        <v>3</v>
+      </c>
+      <c r="D50" s="60">
+        <v>3</v>
+      </c>
+      <c r="E50" s="60">
+        <v>1.4950000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A51" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="60">
+        <v>4.6449999999999996</v>
+      </c>
+      <c r="C51" s="60">
+        <v>5</v>
+      </c>
+      <c r="D51" s="60">
+        <v>5</v>
+      </c>
+      <c r="E51" s="60">
+        <v>0.437</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A52" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="60">
+        <v>2.9350000000000001</v>
+      </c>
+      <c r="C52" s="60">
+        <v>3</v>
+      </c>
+      <c r="D52" s="60">
+        <v>3</v>
+      </c>
+      <c r="E52" s="60">
+        <v>1.7290000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A53" s="59" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="60">
+        <v>3.29</v>
+      </c>
+      <c r="C53" s="60">
+        <v>3</v>
+      </c>
+      <c r="D53" s="60">
+        <v>3</v>
+      </c>
+      <c r="E53" s="60">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A54" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="60">
+        <v>3.387</v>
+      </c>
+      <c r="C54" s="60">
+        <v>3</v>
+      </c>
+      <c r="D54" s="60">
+        <v>3</v>
+      </c>
+      <c r="E54" s="60">
+        <v>1.2450000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A55" s="59" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="60">
+        <v>3.452</v>
+      </c>
+      <c r="C55" s="60">
+        <v>3</v>
+      </c>
+      <c r="D55" s="60">
+        <v>3</v>
+      </c>
+      <c r="E55" s="60">
+        <v>0.78900000000000003</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A56" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="60">
+        <v>3.452</v>
+      </c>
+      <c r="C56" s="60">
+        <v>3</v>
+      </c>
+      <c r="D56" s="60">
+        <v>3</v>
+      </c>
+      <c r="E56" s="60">
+        <v>0.78900000000000003</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A57" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="60">
+        <v>3.548</v>
+      </c>
+      <c r="C57" s="60">
+        <v>4</v>
+      </c>
+      <c r="D57" s="60">
+        <v>4</v>
+      </c>
+      <c r="E57" s="60">
+        <v>0.98899999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A58" s="59" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="60">
+        <v>4.452</v>
+      </c>
+      <c r="C58" s="60">
+        <v>5</v>
+      </c>
+      <c r="D58" s="60">
+        <v>5</v>
+      </c>
+      <c r="E58" s="60">
+        <v>1.256</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A59" s="59" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" s="60">
+        <v>3.097</v>
+      </c>
+      <c r="C59" s="60">
+        <v>3</v>
+      </c>
+      <c r="D59" s="60">
+        <v>3</v>
+      </c>
+      <c r="E59" s="60">
+        <v>2.024</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A60" s="59" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" s="60">
+        <v>3</v>
+      </c>
+      <c r="C60" s="60">
+        <v>3</v>
+      </c>
+      <c r="D60" s="60">
+        <v>3</v>
+      </c>
+      <c r="E60" s="60">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A61" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" s="60">
+        <v>2.839</v>
+      </c>
+      <c r="C61" s="60">
+        <v>3</v>
+      </c>
+      <c r="D61" s="60">
+        <v>3</v>
+      </c>
+      <c r="E61" s="60">
+        <v>1.073</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A62" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" s="60">
+        <v>3.129</v>
+      </c>
+      <c r="C62" s="60">
+        <v>3</v>
+      </c>
+      <c r="D62" s="60">
+        <v>3</v>
+      </c>
+      <c r="E62" s="60">
+        <v>1.2490000000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A63" s="59" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" s="60">
+        <v>3.129</v>
+      </c>
+      <c r="C63" s="60">
+        <v>3</v>
+      </c>
+      <c r="D63" s="60">
+        <v>3</v>
+      </c>
+      <c r="E63" s="60">
+        <v>1.2490000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A64" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" s="60">
+        <v>3.355</v>
+      </c>
+      <c r="C64" s="60">
+        <v>3</v>
+      </c>
+      <c r="D64" s="60">
+        <v>3</v>
+      </c>
+      <c r="E64" s="60">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A65" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" s="60">
+        <v>4.548</v>
+      </c>
+      <c r="C65" s="60">
+        <v>5</v>
+      </c>
+      <c r="D65" s="60">
+        <v>5</v>
+      </c>
+      <c r="E65" s="60">
+        <v>0.78900000000000003</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A66" s="59" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66" s="60">
+        <v>2.871</v>
+      </c>
+      <c r="C66" s="60">
+        <v>3</v>
+      </c>
+      <c r="D66" s="60">
+        <v>3</v>
+      </c>
+      <c r="E66" s="60">
+        <v>1.849</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A67" s="59" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="60">
+        <v>2.677</v>
+      </c>
+      <c r="C67" s="60">
+        <v>3</v>
+      </c>
+      <c r="D67" s="60">
+        <v>3</v>
+      </c>
+      <c r="E67" s="60">
+        <v>1.5589999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A68" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" s="60">
+        <v>2.323</v>
+      </c>
+      <c r="C68" s="60">
+        <v>3</v>
+      </c>
+      <c r="D68" s="60">
+        <v>3</v>
+      </c>
+      <c r="E68" s="60">
+        <v>0.95899999999999996</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A69" s="59" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" s="60">
+        <v>3.161</v>
+      </c>
+      <c r="C69" s="60">
+        <v>3</v>
+      </c>
+      <c r="D69" s="60">
+        <v>4</v>
+      </c>
+      <c r="E69" s="60">
+        <v>1.006</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A70" s="59" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" s="60">
+        <v>3.387</v>
+      </c>
+      <c r="C70" s="60">
+        <v>4</v>
+      </c>
+      <c r="D70" s="60">
+        <v>4</v>
+      </c>
+      <c r="E70" s="60">
+        <v>0.71199999999999997</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A71" s="59" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" s="60">
+        <v>3.484</v>
+      </c>
+      <c r="C71" s="60">
+        <v>4</v>
+      </c>
+      <c r="D71" s="60">
+        <v>4</v>
+      </c>
+      <c r="E71" s="60">
+        <v>0.85799999999999998</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A72" s="59" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" s="60">
+        <v>3.226</v>
+      </c>
+      <c r="C72" s="60">
+        <v>4</v>
+      </c>
+      <c r="D72" s="60">
+        <v>4</v>
+      </c>
+      <c r="E72" s="60">
+        <v>2.181</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A73" s="59" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" s="60">
+        <v>2.032</v>
+      </c>
+      <c r="C73" s="60">
+        <v>1</v>
+      </c>
+      <c r="D73" s="60">
+        <v>1</v>
+      </c>
+      <c r="E73" s="60">
+        <v>1.4990000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A74" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" s="60">
+        <v>3.29</v>
+      </c>
+      <c r="C74" s="60">
+        <v>3</v>
+      </c>
+      <c r="D74" s="60">
+        <v>3</v>
+      </c>
+      <c r="E74" s="60">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A75" s="59" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" s="60">
+        <v>3.419</v>
+      </c>
+      <c r="C75" s="60">
+        <v>3</v>
+      </c>
+      <c r="D75" s="60">
+        <v>3</v>
+      </c>
+      <c r="E75" s="60">
+        <v>1.1850000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A76" s="59" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" s="60">
+        <v>4.0970000000000004</v>
+      </c>
+      <c r="C76" s="60">
+        <v>4</v>
+      </c>
+      <c r="D76" s="60">
+        <v>5</v>
+      </c>
+      <c r="E76" s="60">
+        <v>1.224</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A77" s="59" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" s="60">
+        <v>4.032</v>
+      </c>
+      <c r="C77" s="60">
+        <v>4</v>
+      </c>
+      <c r="D77" s="60">
+        <v>5</v>
+      </c>
+      <c r="E77" s="60">
+        <v>1.232</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="28" x14ac:dyDescent="0.15">
+      <c r="A78" s="59" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" s="60">
+        <v>4.0970000000000004</v>
+      </c>
+      <c r="C78" s="60">
+        <v>4</v>
+      </c>
+      <c r="D78" s="60">
+        <v>5</v>
+      </c>
+      <c r="E78" s="60">
+        <v>1.224</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A354AA-7721-9D4B-A922-4E715083618F}">
+  <dimension ref="A1:BZ27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="3" style="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="11.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="22" customWidth="1"/>
+    <col min="7" max="8" width="11.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="13" style="22" customWidth="1"/>
+    <col min="16" max="20" width="12.83203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13" style="22" customWidth="1"/>
+    <col min="22" max="22" width="12.83203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.5" style="22" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.5" style="22" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="10" style="22" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13" style="22" customWidth="1"/>
+    <col min="28" max="28" width="11.33203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.1640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="30" max="33" width="11.83203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13" style="22" customWidth="1"/>
+    <col min="35" max="36" width="11.83203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.83203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="38" max="40" width="12.33203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13" style="22" customWidth="1"/>
+    <col min="42" max="47" width="12.33203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13" style="22" customWidth="1"/>
+    <col min="49" max="50" width="12.33203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="51" max="54" width="12.5" style="22" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="13" style="22" customWidth="1"/>
+    <col min="56" max="61" width="12.5" style="22" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="13" style="22" customWidth="1"/>
+    <col min="63" max="64" width="12.5" style="22" bestFit="1" customWidth="1"/>
+    <col min="65" max="68" width="12.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="13" style="22" customWidth="1"/>
+    <col min="70" max="78" width="12.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="79" max="16384" width="8.83203125" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:78" ht="165" x14ac:dyDescent="0.15">
+      <c r="A1" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="V1" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="W1" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y1" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z1" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA1" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB1" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC1" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD1" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE1" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF1" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG1" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH1" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI1" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ1" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AK1" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="AL1" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM1" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN1" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO1" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP1" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="AQ1" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="AR1" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="AS1" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="AT1" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="AU1" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="AV1" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="AW1" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="AX1" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="AY1" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="AZ1" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="BA1" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="BB1" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="BC1" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="BD1" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="BE1" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="BF1" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="BG1" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="BH1" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI1" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="BJ1" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="BK1" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="BL1" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="BM1" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="BN1" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="BO1" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="BP1" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="BQ1" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="BR1" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS1" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="BT1" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="BU1" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="BV1" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="BW1" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="BX1" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="BY1" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="BZ1" s="38" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A2" s="40">
+        <v>1</v>
+      </c>
+      <c r="B2" s="39">
+        <v>5</v>
+      </c>
+      <c r="C2" s="39">
+        <v>2</v>
+      </c>
+      <c r="D2" s="39">
+        <v>3</v>
+      </c>
+      <c r="E2" s="39">
+        <v>3</v>
+      </c>
+      <c r="F2" s="39">
+        <v>3</v>
+      </c>
+      <c r="G2" s="39">
+        <v>3</v>
+      </c>
+      <c r="H2" s="39">
+        <v>3</v>
+      </c>
+      <c r="I2" s="39">
+        <v>3</v>
+      </c>
+      <c r="J2" s="39">
+        <v>3</v>
+      </c>
+      <c r="K2" s="39">
+        <v>4</v>
+      </c>
+      <c r="L2" s="39">
+        <v>4</v>
+      </c>
+      <c r="M2" s="39">
+        <v>3</v>
+      </c>
+      <c r="N2" s="39">
+        <v>4</v>
+      </c>
+      <c r="O2" s="39">
+        <v>4</v>
+      </c>
+      <c r="P2" s="39">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="39">
+        <v>2</v>
+      </c>
+      <c r="R2" s="39">
+        <v>2</v>
+      </c>
+      <c r="S2" s="39">
+        <v>2</v>
+      </c>
+      <c r="T2" s="39">
+        <v>2</v>
+      </c>
+      <c r="U2" s="39">
+        <v>2</v>
+      </c>
+      <c r="V2" s="39">
+        <v>2</v>
+      </c>
+      <c r="W2" s="39">
+        <v>3</v>
+      </c>
+      <c r="X2" s="39">
+        <v>3</v>
+      </c>
+      <c r="Y2" s="39">
+        <v>4</v>
+      </c>
+      <c r="Z2" s="39">
+        <v>4</v>
+      </c>
+      <c r="AA2" s="39">
+        <v>3</v>
+      </c>
+      <c r="AB2" s="39">
+        <v>3</v>
+      </c>
+      <c r="AC2" s="39">
+        <v>3</v>
+      </c>
+      <c r="AD2" s="39">
+        <v>4</v>
+      </c>
+      <c r="AE2" s="39">
+        <v>4</v>
+      </c>
+      <c r="AF2" s="39">
+        <v>3</v>
+      </c>
+      <c r="AG2" s="39">
+        <v>3</v>
+      </c>
+      <c r="AH2" s="39">
+        <v>4</v>
+      </c>
+      <c r="AI2" s="39">
+        <v>4</v>
+      </c>
+      <c r="AJ2" s="39">
+        <v>4</v>
+      </c>
+      <c r="AK2" s="39">
+        <v>4</v>
+      </c>
+      <c r="AL2" s="39">
+        <v>4</v>
+      </c>
+      <c r="AM2" s="39">
+        <v>3</v>
+      </c>
+      <c r="AN2" s="39">
+        <v>2</v>
+      </c>
+      <c r="AO2" s="39">
+        <v>3</v>
+      </c>
+      <c r="AP2" s="39">
+        <v>3</v>
+      </c>
+      <c r="AQ2" s="39">
+        <v>3</v>
+      </c>
+      <c r="AR2" s="39">
+        <v>4</v>
+      </c>
+      <c r="AS2" s="39">
+        <v>1</v>
+      </c>
+      <c r="AT2" s="39">
+        <v>4</v>
+      </c>
+      <c r="AU2" s="39">
+        <v>4</v>
+      </c>
+      <c r="AV2" s="39">
+        <v>4</v>
+      </c>
+      <c r="AW2" s="39">
+        <v>4</v>
+      </c>
+      <c r="AX2" s="39">
+        <v>4</v>
+      </c>
+      <c r="AY2" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ2" s="39">
+        <v>2</v>
+      </c>
+      <c r="BA2" s="39">
+        <v>3</v>
+      </c>
+      <c r="BB2" s="39">
+        <v>2</v>
+      </c>
+      <c r="BC2" s="39">
+        <v>3</v>
+      </c>
+      <c r="BD2" s="39">
+        <v>3</v>
+      </c>
+      <c r="BE2" s="39">
+        <v>3</v>
+      </c>
+      <c r="BF2" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG2" s="39">
+        <v>3</v>
+      </c>
+      <c r="BH2" s="39">
+        <v>2</v>
+      </c>
+      <c r="BI2" s="39">
+        <v>1</v>
+      </c>
+      <c r="BJ2" s="39">
+        <v>4</v>
+      </c>
+      <c r="BK2" s="39">
+        <v>4</v>
+      </c>
+      <c r="BL2" s="39">
+        <v>4</v>
+      </c>
+      <c r="BM2" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN2" s="39">
+        <v>3</v>
+      </c>
+      <c r="BO2" s="39">
+        <v>2</v>
+      </c>
+      <c r="BP2" s="39">
+        <v>1</v>
+      </c>
+      <c r="BQ2" s="39">
+        <v>3</v>
+      </c>
+      <c r="BR2" s="39">
+        <v>3</v>
+      </c>
+      <c r="BS2" s="39">
+        <v>3</v>
+      </c>
+      <c r="BT2" s="39">
+        <v>1</v>
+      </c>
+      <c r="BU2" s="39">
+        <v>1</v>
+      </c>
+      <c r="BV2" s="39">
+        <v>2</v>
+      </c>
+      <c r="BW2" s="39">
+        <v>4</v>
+      </c>
+      <c r="BX2" s="39">
+        <v>4</v>
+      </c>
+      <c r="BY2" s="39">
+        <v>4</v>
+      </c>
+      <c r="BZ2" s="39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A3" s="40">
+        <v>2</v>
+      </c>
+      <c r="B3" s="39">
+        <v>5</v>
+      </c>
+      <c r="C3" s="39">
+        <v>4</v>
+      </c>
+      <c r="D3" s="39">
+        <v>4</v>
+      </c>
+      <c r="E3" s="39">
+        <v>3</v>
+      </c>
+      <c r="F3" s="39">
+        <v>4</v>
+      </c>
+      <c r="G3" s="39">
+        <v>1</v>
+      </c>
+      <c r="H3" s="39">
+        <v>4</v>
+      </c>
+      <c r="I3" s="39">
+        <v>4</v>
+      </c>
+      <c r="J3" s="39">
+        <v>4</v>
+      </c>
+      <c r="K3" s="39">
+        <v>5</v>
+      </c>
+      <c r="L3" s="39">
+        <v>5</v>
+      </c>
+      <c r="M3" s="39">
+        <v>5</v>
+      </c>
+      <c r="N3" s="39">
+        <v>1</v>
+      </c>
+      <c r="O3" s="39">
+        <v>5</v>
+      </c>
+      <c r="P3" s="39">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="39">
+        <v>4</v>
+      </c>
+      <c r="R3" s="39">
+        <v>5</v>
+      </c>
+      <c r="S3" s="39">
+        <v>3</v>
+      </c>
+      <c r="T3" s="39">
+        <v>5</v>
+      </c>
+      <c r="U3" s="39">
+        <v>1</v>
+      </c>
+      <c r="V3" s="39">
+        <v>5</v>
+      </c>
+      <c r="W3" s="39">
+        <v>4</v>
+      </c>
+      <c r="X3" s="39">
+        <v>5</v>
+      </c>
+      <c r="Y3" s="39">
+        <v>5</v>
+      </c>
+      <c r="Z3" s="39">
+        <v>5</v>
+      </c>
+      <c r="AA3" s="39">
+        <v>4</v>
+      </c>
+      <c r="AB3" s="39">
+        <v>3</v>
+      </c>
+      <c r="AC3" s="39">
+        <v>4</v>
+      </c>
+      <c r="AD3" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE3" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF3" s="39">
+        <v>5</v>
+      </c>
+      <c r="AG3" s="39">
+        <v>5</v>
+      </c>
+      <c r="AH3" s="39">
+        <v>5</v>
+      </c>
+      <c r="AI3" s="39">
+        <v>3</v>
+      </c>
+      <c r="AJ3" s="39">
+        <v>4</v>
+      </c>
+      <c r="AK3" s="39">
+        <v>5</v>
+      </c>
+      <c r="AL3" s="39">
+        <v>5</v>
+      </c>
+      <c r="AM3" s="39">
+        <v>3</v>
+      </c>
+      <c r="AN3" s="39">
+        <v>3</v>
+      </c>
+      <c r="AO3" s="39">
+        <v>5</v>
+      </c>
+      <c r="AP3" s="39">
+        <v>3</v>
+      </c>
+      <c r="AQ3" s="39">
+        <v>3</v>
+      </c>
+      <c r="AR3" s="39">
+        <v>4</v>
+      </c>
+      <c r="AS3" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT3" s="39">
+        <v>5</v>
+      </c>
+      <c r="AU3" s="39">
+        <v>3</v>
+      </c>
+      <c r="AV3" s="39">
+        <v>4</v>
+      </c>
+      <c r="AW3" s="39">
+        <v>4</v>
+      </c>
+      <c r="AX3" s="39">
+        <v>4</v>
+      </c>
+      <c r="AY3" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ3" s="39">
+        <v>4</v>
+      </c>
+      <c r="BA3" s="39">
+        <v>5</v>
+      </c>
+      <c r="BB3" s="39">
+        <v>3</v>
+      </c>
+      <c r="BC3" s="39">
+        <v>4</v>
+      </c>
+      <c r="BD3" s="39">
+        <v>3</v>
+      </c>
+      <c r="BE3" s="39">
+        <v>4</v>
+      </c>
+      <c r="BF3" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG3" s="39">
+        <v>2</v>
+      </c>
+      <c r="BH3" s="39">
+        <v>4</v>
+      </c>
+      <c r="BI3" s="39">
+        <v>3</v>
+      </c>
+      <c r="BJ3" s="39">
+        <v>3</v>
+      </c>
+      <c r="BK3" s="39">
+        <v>1</v>
+      </c>
+      <c r="BL3" s="39">
+        <v>4</v>
+      </c>
+      <c r="BM3" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN3" s="39">
+        <v>3</v>
+      </c>
+      <c r="BO3" s="39">
+        <v>4</v>
+      </c>
+      <c r="BP3" s="39">
+        <v>3</v>
+      </c>
+      <c r="BQ3" s="39">
+        <v>3</v>
+      </c>
+      <c r="BR3" s="39">
+        <v>3</v>
+      </c>
+      <c r="BS3" s="39">
+        <v>3</v>
+      </c>
+      <c r="BT3" s="39">
+        <v>5</v>
+      </c>
+      <c r="BU3" s="39">
+        <v>1</v>
+      </c>
+      <c r="BV3" s="39">
+        <v>5</v>
+      </c>
+      <c r="BW3" s="39">
+        <v>3</v>
+      </c>
+      <c r="BX3" s="39">
+        <v>5</v>
+      </c>
+      <c r="BY3" s="39">
+        <v>5</v>
+      </c>
+      <c r="BZ3" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A4" s="40">
+        <v>5</v>
+      </c>
+      <c r="B4" s="39">
+        <v>5</v>
+      </c>
+      <c r="C4" s="39">
+        <v>5</v>
+      </c>
+      <c r="D4" s="39">
+        <v>4</v>
+      </c>
+      <c r="E4" s="39">
+        <v>3</v>
+      </c>
+      <c r="F4" s="39">
+        <v>3</v>
+      </c>
+      <c r="G4" s="39">
+        <v>4</v>
+      </c>
+      <c r="H4" s="39">
+        <v>3</v>
+      </c>
+      <c r="I4" s="39">
+        <v>5</v>
+      </c>
+      <c r="J4" s="39">
+        <v>4</v>
+      </c>
+      <c r="K4" s="39">
+        <v>5</v>
+      </c>
+      <c r="L4" s="39">
+        <v>4</v>
+      </c>
+      <c r="M4" s="39">
+        <v>5</v>
+      </c>
+      <c r="N4" s="39">
+        <v>5</v>
+      </c>
+      <c r="O4" s="39">
+        <v>5</v>
+      </c>
+      <c r="P4" s="39">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="39">
+        <v>5</v>
+      </c>
+      <c r="R4" s="39">
+        <v>4</v>
+      </c>
+      <c r="S4" s="39">
+        <v>4</v>
+      </c>
+      <c r="T4" s="39">
+        <v>4</v>
+      </c>
+      <c r="U4" s="39">
+        <v>4</v>
+      </c>
+      <c r="V4" s="39">
+        <v>4</v>
+      </c>
+      <c r="W4" s="39">
+        <v>4</v>
+      </c>
+      <c r="X4" s="39">
+        <v>4</v>
+      </c>
+      <c r="Y4" s="39">
+        <v>5</v>
+      </c>
+      <c r="Z4" s="39">
+        <v>4</v>
+      </c>
+      <c r="AA4" s="39">
+        <v>4</v>
+      </c>
+      <c r="AB4" s="39">
+        <v>4</v>
+      </c>
+      <c r="AC4" s="39">
+        <v>4</v>
+      </c>
+      <c r="AD4" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE4" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF4" s="39">
+        <v>4</v>
+      </c>
+      <c r="AG4" s="39">
+        <v>3</v>
+      </c>
+      <c r="AH4" s="39">
+        <v>4</v>
+      </c>
+      <c r="AI4" s="39">
+        <v>4</v>
+      </c>
+      <c r="AJ4" s="39">
+        <v>4</v>
+      </c>
+      <c r="AK4" s="39">
+        <v>5</v>
+      </c>
+      <c r="AL4" s="39">
+        <v>4</v>
+      </c>
+      <c r="AM4" s="39">
+        <v>4</v>
+      </c>
+      <c r="AN4" s="39">
+        <v>4</v>
+      </c>
+      <c r="AO4" s="39">
+        <v>5</v>
+      </c>
+      <c r="AP4" s="39">
+        <v>5</v>
+      </c>
+      <c r="AQ4" s="39">
+        <v>5</v>
+      </c>
+      <c r="AR4" s="39">
+        <v>2</v>
+      </c>
+      <c r="AS4" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT4" s="39">
+        <v>3</v>
+      </c>
+      <c r="AU4" s="39">
+        <v>3</v>
+      </c>
+      <c r="AV4" s="39">
+        <v>2</v>
+      </c>
+      <c r="AW4" s="39">
+        <v>2</v>
+      </c>
+      <c r="AX4" s="39">
+        <v>2</v>
+      </c>
+      <c r="AY4" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ4" s="39">
+        <v>4</v>
+      </c>
+      <c r="BA4" s="39">
+        <v>5</v>
+      </c>
+      <c r="BB4" s="39">
+        <v>4</v>
+      </c>
+      <c r="BC4" s="39">
+        <v>4</v>
+      </c>
+      <c r="BD4" s="39">
+        <v>4</v>
+      </c>
+      <c r="BE4" s="39">
+        <v>4</v>
+      </c>
+      <c r="BF4" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG4" s="39">
+        <v>5</v>
+      </c>
+      <c r="BH4" s="39">
+        <v>3</v>
+      </c>
+      <c r="BI4" s="39">
+        <v>4</v>
+      </c>
+      <c r="BJ4" s="39">
+        <v>3</v>
+      </c>
+      <c r="BK4" s="39">
+        <v>3</v>
+      </c>
+      <c r="BL4" s="39">
+        <v>3</v>
+      </c>
+      <c r="BM4" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN4" s="39">
+        <v>4</v>
+      </c>
+      <c r="BO4" s="39">
+        <v>3</v>
+      </c>
+      <c r="BP4" s="39">
+        <v>3</v>
+      </c>
+      <c r="BQ4" s="39">
+        <v>3</v>
+      </c>
+      <c r="BR4" s="39">
+        <v>4</v>
+      </c>
+      <c r="BS4" s="39">
+        <v>3</v>
+      </c>
+      <c r="BT4" s="39">
+        <v>3</v>
+      </c>
+      <c r="BU4" s="39">
+        <v>2</v>
+      </c>
+      <c r="BV4" s="39">
+        <v>4</v>
+      </c>
+      <c r="BW4" s="39">
+        <v>4</v>
+      </c>
+      <c r="BX4" s="39">
+        <v>5</v>
+      </c>
+      <c r="BY4" s="39">
+        <v>5</v>
+      </c>
+      <c r="BZ4" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A5" s="40">
+        <v>6</v>
+      </c>
+      <c r="B5" s="39">
+        <v>3</v>
+      </c>
+      <c r="C5" s="39">
+        <v>5</v>
+      </c>
+      <c r="D5" s="39">
+        <v>4</v>
+      </c>
+      <c r="E5" s="39">
+        <v>4</v>
+      </c>
+      <c r="F5" s="39">
+        <v>3</v>
+      </c>
+      <c r="G5" s="39">
+        <v>3</v>
+      </c>
+      <c r="H5" s="39">
+        <v>3</v>
+      </c>
+      <c r="I5" s="39">
+        <v>4</v>
+      </c>
+      <c r="J5" s="39">
+        <v>4</v>
+      </c>
+      <c r="K5" s="39">
+        <v>5</v>
+      </c>
+      <c r="L5" s="39">
+        <v>5</v>
+      </c>
+      <c r="M5" s="39">
+        <v>4</v>
+      </c>
+      <c r="N5" s="39">
+        <v>4</v>
+      </c>
+      <c r="O5" s="39">
+        <v>4</v>
+      </c>
+      <c r="P5" s="39">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="39">
+        <v>4</v>
+      </c>
+      <c r="R5" s="39">
+        <v>3</v>
+      </c>
+      <c r="S5" s="39">
+        <v>2</v>
+      </c>
+      <c r="T5" s="39">
+        <v>2</v>
+      </c>
+      <c r="U5" s="39">
+        <v>2</v>
+      </c>
+      <c r="V5" s="39">
+        <v>2</v>
+      </c>
+      <c r="W5" s="39">
+        <v>2</v>
+      </c>
+      <c r="X5" s="39">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="39">
+        <v>5</v>
+      </c>
+      <c r="Z5" s="39">
+        <v>5</v>
+      </c>
+      <c r="AA5" s="39">
+        <v>3</v>
+      </c>
+      <c r="AB5" s="39">
+        <v>3</v>
+      </c>
+      <c r="AC5" s="39">
+        <v>3</v>
+      </c>
+      <c r="AD5" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE5" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF5" s="39">
+        <v>3</v>
+      </c>
+      <c r="AG5" s="39">
+        <v>2</v>
+      </c>
+      <c r="AH5" s="39">
+        <v>4</v>
+      </c>
+      <c r="AI5" s="39">
+        <v>4</v>
+      </c>
+      <c r="AJ5" s="39">
+        <v>4</v>
+      </c>
+      <c r="AK5" s="39">
+        <v>5</v>
+      </c>
+      <c r="AL5" s="39">
+        <v>4</v>
+      </c>
+      <c r="AM5" s="39">
+        <v>2</v>
+      </c>
+      <c r="AN5" s="39">
+        <v>2</v>
+      </c>
+      <c r="AO5" s="39">
+        <v>3</v>
+      </c>
+      <c r="AP5" s="39">
+        <v>3</v>
+      </c>
+      <c r="AQ5" s="39">
+        <v>3</v>
+      </c>
+      <c r="AR5" s="39">
+        <v>3</v>
+      </c>
+      <c r="AS5" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT5" s="39">
+        <v>2</v>
+      </c>
+      <c r="AU5" s="39">
+        <v>2</v>
+      </c>
+      <c r="AV5" s="39">
+        <v>3</v>
+      </c>
+      <c r="AW5" s="39">
+        <v>3</v>
+      </c>
+      <c r="AX5" s="39">
+        <v>3</v>
+      </c>
+      <c r="AY5" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ5" s="39">
+        <v>5</v>
+      </c>
+      <c r="BA5" s="39">
+        <v>3</v>
+      </c>
+      <c r="BB5" s="39">
+        <v>3</v>
+      </c>
+      <c r="BC5" s="39">
+        <v>4</v>
+      </c>
+      <c r="BD5" s="39">
+        <v>4</v>
+      </c>
+      <c r="BE5" s="39">
+        <v>4</v>
+      </c>
+      <c r="BF5" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG5" s="39">
+        <v>5</v>
+      </c>
+      <c r="BH5" s="39">
+        <v>3</v>
+      </c>
+      <c r="BI5" s="39">
+        <v>3</v>
+      </c>
+      <c r="BJ5" s="39">
+        <v>4</v>
+      </c>
+      <c r="BK5" s="39">
+        <v>4</v>
+      </c>
+      <c r="BL5" s="39">
+        <v>4</v>
+      </c>
+      <c r="BM5" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN5" s="39">
+        <v>5</v>
+      </c>
+      <c r="BO5" s="39">
+        <v>3</v>
+      </c>
+      <c r="BP5" s="39">
+        <v>3</v>
+      </c>
+      <c r="BQ5" s="39">
+        <v>4</v>
+      </c>
+      <c r="BR5" s="39">
+        <v>4</v>
+      </c>
+      <c r="BS5" s="39">
+        <v>4</v>
+      </c>
+      <c r="BT5" s="39">
+        <v>4</v>
+      </c>
+      <c r="BU5" s="39">
+        <v>4</v>
+      </c>
+      <c r="BV5" s="39">
+        <v>5</v>
+      </c>
+      <c r="BW5" s="39">
+        <v>3</v>
+      </c>
+      <c r="BX5" s="39">
+        <v>5</v>
+      </c>
+      <c r="BY5" s="39">
+        <v>5</v>
+      </c>
+      <c r="BZ5" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A6" s="40">
+        <v>7</v>
+      </c>
+      <c r="B6" s="39">
+        <v>4</v>
+      </c>
+      <c r="C6" s="39">
+        <v>2</v>
+      </c>
+      <c r="D6" s="39">
+        <v>3</v>
+      </c>
+      <c r="E6" s="39">
+        <v>4</v>
+      </c>
+      <c r="F6" s="39">
+        <v>3</v>
+      </c>
+      <c r="G6" s="39">
+        <v>3</v>
+      </c>
+      <c r="H6" s="39">
+        <v>3</v>
+      </c>
+      <c r="I6" s="39">
+        <v>4</v>
+      </c>
+      <c r="J6" s="39">
+        <v>3</v>
+      </c>
+      <c r="K6" s="39">
+        <v>5</v>
+      </c>
+      <c r="L6" s="39">
+        <v>5</v>
+      </c>
+      <c r="M6" s="39">
+        <v>4</v>
+      </c>
+      <c r="N6" s="39">
+        <v>4</v>
+      </c>
+      <c r="O6" s="39">
+        <v>4</v>
+      </c>
+      <c r="P6" s="39">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="39">
+        <v>2</v>
+      </c>
+      <c r="R6" s="39">
+        <v>4</v>
+      </c>
+      <c r="S6" s="39">
+        <v>4</v>
+      </c>
+      <c r="T6" s="39">
+        <v>5</v>
+      </c>
+      <c r="U6" s="39">
+        <v>5</v>
+      </c>
+      <c r="V6" s="39">
+        <v>5</v>
+      </c>
+      <c r="W6" s="39">
+        <v>3</v>
+      </c>
+      <c r="X6" s="39">
+        <v>3</v>
+      </c>
+      <c r="Y6" s="39">
+        <v>5</v>
+      </c>
+      <c r="Z6" s="39">
+        <v>5</v>
+      </c>
+      <c r="AA6" s="39">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="39">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="39">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE6" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF6" s="39">
+        <v>2</v>
+      </c>
+      <c r="AG6" s="39">
+        <v>2</v>
+      </c>
+      <c r="AH6" s="39">
+        <v>3</v>
+      </c>
+      <c r="AI6" s="39">
+        <v>4</v>
+      </c>
+      <c r="AJ6" s="39">
+        <v>4</v>
+      </c>
+      <c r="AK6" s="39">
+        <v>5</v>
+      </c>
+      <c r="AL6" s="39">
+        <v>5</v>
+      </c>
+      <c r="AM6" s="39">
+        <v>3</v>
+      </c>
+      <c r="AN6" s="39">
+        <v>2</v>
+      </c>
+      <c r="AO6" s="39">
+        <v>5</v>
+      </c>
+      <c r="AP6" s="39">
+        <v>5</v>
+      </c>
+      <c r="AQ6" s="39">
+        <v>5</v>
+      </c>
+      <c r="AR6" s="39">
+        <v>2</v>
+      </c>
+      <c r="AS6" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT6" s="39">
+        <v>4</v>
+      </c>
+      <c r="AU6" s="39">
+        <v>4</v>
+      </c>
+      <c r="AV6" s="39">
+        <v>2</v>
+      </c>
+      <c r="AW6" s="39">
+        <v>2</v>
+      </c>
+      <c r="AX6" s="39">
+        <v>2</v>
+      </c>
+      <c r="AY6" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ6" s="39">
+        <v>1</v>
+      </c>
+      <c r="BA6" s="39">
+        <v>2</v>
+      </c>
+      <c r="BB6" s="39">
+        <v>3</v>
+      </c>
+      <c r="BC6" s="39">
+        <v>4</v>
+      </c>
+      <c r="BD6" s="39">
+        <v>4</v>
+      </c>
+      <c r="BE6" s="39">
+        <v>4</v>
+      </c>
+      <c r="BF6" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG6" s="39">
+        <v>1</v>
+      </c>
+      <c r="BH6" s="39">
+        <v>2</v>
+      </c>
+      <c r="BI6" s="39">
+        <v>4</v>
+      </c>
+      <c r="BJ6" s="39">
+        <v>3</v>
+      </c>
+      <c r="BK6" s="39">
+        <v>3</v>
+      </c>
+      <c r="BL6" s="39">
+        <v>3</v>
+      </c>
+      <c r="BM6" s="39">
+        <v>4</v>
+      </c>
+      <c r="BN6" s="39">
+        <v>2</v>
+      </c>
+      <c r="BO6" s="39">
+        <v>2</v>
+      </c>
+      <c r="BP6" s="39">
+        <v>2</v>
+      </c>
+      <c r="BQ6" s="39">
+        <v>4</v>
+      </c>
+      <c r="BR6" s="39">
+        <v>4</v>
+      </c>
+      <c r="BS6" s="39">
+        <v>4</v>
+      </c>
+      <c r="BT6" s="39">
+        <v>4</v>
+      </c>
+      <c r="BU6" s="39">
+        <v>1</v>
+      </c>
+      <c r="BV6" s="39">
+        <v>3</v>
+      </c>
+      <c r="BW6" s="39">
+        <v>5</v>
+      </c>
+      <c r="BX6" s="39">
+        <v>4</v>
+      </c>
+      <c r="BY6" s="39">
+        <v>4</v>
+      </c>
+      <c r="BZ6" s="39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A7" s="40">
+        <v>8</v>
+      </c>
+      <c r="B7" s="39">
+        <v>4</v>
+      </c>
+      <c r="C7" s="39">
+        <v>3</v>
+      </c>
+      <c r="D7" s="39">
+        <v>4</v>
+      </c>
+      <c r="E7" s="39">
+        <v>4</v>
+      </c>
+      <c r="F7" s="39">
+        <v>4</v>
+      </c>
+      <c r="G7" s="39">
+        <v>4</v>
+      </c>
+      <c r="H7" s="39">
+        <v>4</v>
+      </c>
+      <c r="I7" s="39">
+        <v>3</v>
+      </c>
+      <c r="J7" s="39">
+        <v>2</v>
+      </c>
+      <c r="K7" s="39">
+        <v>5</v>
+      </c>
+      <c r="L7" s="39">
+        <v>5</v>
+      </c>
+      <c r="M7" s="39">
+        <v>4</v>
+      </c>
+      <c r="N7" s="39">
+        <v>4</v>
+      </c>
+      <c r="O7" s="39">
+        <v>4</v>
+      </c>
+      <c r="P7" s="39">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="39">
+        <v>1</v>
+      </c>
+      <c r="R7" s="39">
+        <v>4</v>
+      </c>
+      <c r="S7" s="39">
+        <v>4</v>
+      </c>
+      <c r="T7" s="39">
+        <v>4</v>
+      </c>
+      <c r="U7" s="39">
+        <v>4</v>
+      </c>
+      <c r="V7" s="39">
+        <v>4</v>
+      </c>
+      <c r="W7" s="39">
+        <v>2</v>
+      </c>
+      <c r="X7" s="39">
+        <v>2</v>
+      </c>
+      <c r="Y7" s="39">
+        <v>5</v>
+      </c>
+      <c r="Z7" s="39">
+        <v>5</v>
+      </c>
+      <c r="AA7" s="39">
+        <v>2</v>
+      </c>
+      <c r="AB7" s="39">
+        <v>3</v>
+      </c>
+      <c r="AC7" s="39">
+        <v>4</v>
+      </c>
+      <c r="AD7" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE7" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF7" s="39">
+        <v>4</v>
+      </c>
+      <c r="AG7" s="39">
+        <v>3</v>
+      </c>
+      <c r="AH7" s="39">
+        <v>5</v>
+      </c>
+      <c r="AI7" s="39">
+        <v>5</v>
+      </c>
+      <c r="AJ7" s="39">
+        <v>5</v>
+      </c>
+      <c r="AK7" s="39">
+        <v>4</v>
+      </c>
+      <c r="AL7" s="39">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="39">
+        <v>3</v>
+      </c>
+      <c r="AN7" s="39">
+        <v>3</v>
+      </c>
+      <c r="AO7" s="39">
+        <v>3</v>
+      </c>
+      <c r="AP7" s="39">
+        <v>3</v>
+      </c>
+      <c r="AQ7" s="39">
+        <v>4</v>
+      </c>
+      <c r="AR7" s="39">
+        <v>2</v>
+      </c>
+      <c r="AS7" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT7" s="39">
+        <v>5</v>
+      </c>
+      <c r="AU7" s="39">
+        <v>4</v>
+      </c>
+      <c r="AV7" s="39">
+        <v>2</v>
+      </c>
+      <c r="AW7" s="39">
+        <v>2</v>
+      </c>
+      <c r="AX7" s="39">
+        <v>2</v>
+      </c>
+      <c r="AY7" s="39">
+        <v>4</v>
+      </c>
+      <c r="AZ7" s="39">
+        <v>1</v>
+      </c>
+      <c r="BA7" s="39">
+        <v>4</v>
+      </c>
+      <c r="BB7" s="39">
+        <v>4</v>
+      </c>
+      <c r="BC7" s="39">
+        <v>4</v>
+      </c>
+      <c r="BD7" s="39">
+        <v>4</v>
+      </c>
+      <c r="BE7" s="39">
+        <v>4</v>
+      </c>
+      <c r="BF7" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG7" s="39">
+        <v>2</v>
+      </c>
+      <c r="BH7" s="39">
+        <v>3</v>
+      </c>
+      <c r="BI7" s="39">
+        <v>4</v>
+      </c>
+      <c r="BJ7" s="39">
+        <v>3</v>
+      </c>
+      <c r="BK7" s="39">
+        <v>3</v>
+      </c>
+      <c r="BL7" s="39">
+        <v>3</v>
+      </c>
+      <c r="BM7" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN7" s="39">
+        <v>2</v>
+      </c>
+      <c r="BO7" s="39">
+        <v>3</v>
+      </c>
+      <c r="BP7" s="39">
+        <v>3</v>
+      </c>
+      <c r="BQ7" s="39">
+        <v>4</v>
+      </c>
+      <c r="BR7" s="39">
+        <v>4</v>
+      </c>
+      <c r="BS7" s="39">
+        <v>4</v>
+      </c>
+      <c r="BT7" s="39">
+        <v>4</v>
+      </c>
+      <c r="BU7" s="39">
+        <v>1</v>
+      </c>
+      <c r="BV7" s="39">
+        <v>2</v>
+      </c>
+      <c r="BW7" s="39">
+        <v>2</v>
+      </c>
+      <c r="BX7" s="39">
+        <v>5</v>
+      </c>
+      <c r="BY7" s="39">
+        <v>5</v>
+      </c>
+      <c r="BZ7" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A8" s="40">
+        <v>9</v>
+      </c>
+      <c r="B8" s="39">
+        <v>4</v>
+      </c>
+      <c r="C8" s="39">
+        <v>4</v>
+      </c>
+      <c r="D8" s="39">
+        <v>2</v>
+      </c>
+      <c r="E8" s="39">
+        <v>3</v>
+      </c>
+      <c r="F8" s="39">
+        <v>3</v>
+      </c>
+      <c r="G8" s="39">
+        <v>3</v>
+      </c>
+      <c r="H8" s="39">
+        <v>3</v>
+      </c>
+      <c r="I8" s="39">
+        <v>4</v>
+      </c>
+      <c r="J8" s="39">
+        <v>4</v>
+      </c>
+      <c r="K8" s="39">
+        <v>4</v>
+      </c>
+      <c r="L8" s="39">
+        <v>4</v>
+      </c>
+      <c r="M8" s="39">
+        <v>2</v>
+      </c>
+      <c r="N8" s="39">
+        <v>2</v>
+      </c>
+      <c r="O8" s="39">
+        <v>2</v>
+      </c>
+      <c r="P8" s="39">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="39">
+        <v>4</v>
+      </c>
+      <c r="R8" s="39">
+        <v>2</v>
+      </c>
+      <c r="S8" s="39">
+        <v>3</v>
+      </c>
+      <c r="T8" s="39">
+        <v>3</v>
+      </c>
+      <c r="U8" s="39">
+        <v>3</v>
+      </c>
+      <c r="V8" s="39">
+        <v>3</v>
+      </c>
+      <c r="W8" s="39">
+        <v>4</v>
+      </c>
+      <c r="X8" s="39">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="39">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="39">
+        <v>4</v>
+      </c>
+      <c r="AA8" s="39">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="39">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="39">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE8" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF8" s="39">
+        <v>3</v>
+      </c>
+      <c r="AG8" s="39">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="39">
+        <v>4</v>
+      </c>
+      <c r="AI8" s="39">
+        <v>3</v>
+      </c>
+      <c r="AJ8" s="39">
+        <v>3</v>
+      </c>
+      <c r="AK8" s="39">
+        <v>5</v>
+      </c>
+      <c r="AL8" s="39">
+        <v>4</v>
+      </c>
+      <c r="AM8" s="39">
+        <v>2</v>
+      </c>
+      <c r="AN8" s="39">
+        <v>2</v>
+      </c>
+      <c r="AO8" s="39">
+        <v>3</v>
+      </c>
+      <c r="AP8" s="39">
+        <v>3</v>
+      </c>
+      <c r="AQ8" s="39">
+        <v>3</v>
+      </c>
+      <c r="AR8" s="39">
+        <v>5</v>
+      </c>
+      <c r="AS8" s="39">
+        <v>2</v>
+      </c>
+      <c r="AT8" s="39">
+        <v>4</v>
+      </c>
+      <c r="AU8" s="39">
+        <v>4</v>
+      </c>
+      <c r="AV8" s="39">
+        <v>4</v>
+      </c>
+      <c r="AW8" s="39">
+        <v>4</v>
+      </c>
+      <c r="AX8" s="39">
+        <v>4</v>
+      </c>
+      <c r="AY8" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ8" s="39">
+        <v>4</v>
+      </c>
+      <c r="BA8" s="39">
+        <v>2</v>
+      </c>
+      <c r="BB8" s="39">
+        <v>2</v>
+      </c>
+      <c r="BC8" s="39">
+        <v>3</v>
+      </c>
+      <c r="BD8" s="39">
+        <v>3</v>
+      </c>
+      <c r="BE8" s="39">
+        <v>3</v>
+      </c>
+      <c r="BF8" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG8" s="39">
+        <v>5</v>
+      </c>
+      <c r="BH8" s="39">
+        <v>2</v>
+      </c>
+      <c r="BI8" s="39">
+        <v>2</v>
+      </c>
+      <c r="BJ8" s="39">
+        <v>3</v>
+      </c>
+      <c r="BK8" s="39">
+        <v>3</v>
+      </c>
+      <c r="BL8" s="39">
+        <v>3</v>
+      </c>
+      <c r="BM8" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN8" s="39">
+        <v>4</v>
+      </c>
+      <c r="BO8" s="39">
+        <v>1</v>
+      </c>
+      <c r="BP8" s="39">
+        <v>1</v>
+      </c>
+      <c r="BQ8" s="39">
+        <v>4</v>
+      </c>
+      <c r="BR8" s="39">
+        <v>4</v>
+      </c>
+      <c r="BS8" s="39">
+        <v>4</v>
+      </c>
+      <c r="BT8" s="39">
+        <v>2</v>
+      </c>
+      <c r="BU8" s="39">
+        <v>2</v>
+      </c>
+      <c r="BV8" s="39">
+        <v>2</v>
+      </c>
+      <c r="BW8" s="39">
+        <v>2</v>
+      </c>
+      <c r="BX8" s="39">
+        <v>5</v>
+      </c>
+      <c r="BY8" s="39">
+        <v>5</v>
+      </c>
+      <c r="BZ8" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A9" s="40">
+        <v>10</v>
+      </c>
+      <c r="B9" s="39">
+        <v>5</v>
+      </c>
+      <c r="C9" s="39">
+        <v>4</v>
+      </c>
+      <c r="D9" s="39">
+        <v>2</v>
+      </c>
+      <c r="E9" s="39">
+        <v>4</v>
+      </c>
+      <c r="F9" s="39">
+        <v>3</v>
+      </c>
+      <c r="G9" s="39">
+        <v>3</v>
+      </c>
+      <c r="H9" s="39">
+        <v>5</v>
+      </c>
+      <c r="I9" s="39">
+        <v>5</v>
+      </c>
+      <c r="J9" s="39">
+        <v>5</v>
+      </c>
+      <c r="K9" s="39">
+        <v>5</v>
+      </c>
+      <c r="L9" s="39">
+        <v>5</v>
+      </c>
+      <c r="M9" s="39">
+        <v>5</v>
+      </c>
+      <c r="N9" s="39">
+        <v>5</v>
+      </c>
+      <c r="O9" s="39">
+        <v>5</v>
+      </c>
+      <c r="P9" s="39">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="39">
+        <v>5</v>
+      </c>
+      <c r="R9" s="39">
+        <v>3</v>
+      </c>
+      <c r="S9" s="39">
+        <v>4</v>
+      </c>
+      <c r="T9" s="39">
+        <v>4</v>
+      </c>
+      <c r="U9" s="39">
+        <v>5</v>
+      </c>
+      <c r="V9" s="39">
+        <v>5</v>
+      </c>
+      <c r="W9" s="39">
+        <v>4</v>
+      </c>
+      <c r="X9" s="39">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="39">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="39">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="39">
+        <v>4</v>
+      </c>
+      <c r="AB9" s="39">
+        <v>4</v>
+      </c>
+      <c r="AC9" s="39">
+        <v>4</v>
+      </c>
+      <c r="AD9" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="39">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="39">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="39">
+        <v>5</v>
+      </c>
+      <c r="AI9" s="39">
+        <v>1</v>
+      </c>
+      <c r="AJ9" s="39">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="39">
+        <v>4</v>
+      </c>
+      <c r="AL9" s="39">
+        <v>5</v>
+      </c>
+      <c r="AM9" s="39">
+        <v>4</v>
+      </c>
+      <c r="AN9" s="39">
+        <v>2</v>
+      </c>
+      <c r="AO9" s="39">
+        <v>3</v>
+      </c>
+      <c r="AP9" s="39">
+        <v>1</v>
+      </c>
+      <c r="AQ9" s="39">
+        <v>5</v>
+      </c>
+      <c r="AR9" s="39">
+        <v>4</v>
+      </c>
+      <c r="AS9" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT9" s="39">
+        <v>2</v>
+      </c>
+      <c r="AU9" s="39">
+        <v>2</v>
+      </c>
+      <c r="AV9" s="39">
+        <v>4</v>
+      </c>
+      <c r="AW9" s="39">
+        <v>4</v>
+      </c>
+      <c r="AX9" s="39">
+        <v>4</v>
+      </c>
+      <c r="AY9" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ9" s="39">
+        <v>3</v>
+      </c>
+      <c r="BA9" s="39">
+        <v>2</v>
+      </c>
+      <c r="BB9" s="39">
+        <v>5</v>
+      </c>
+      <c r="BC9" s="39">
+        <v>4</v>
+      </c>
+      <c r="BD9" s="39">
+        <v>4</v>
+      </c>
+      <c r="BE9" s="39">
+        <v>5</v>
+      </c>
+      <c r="BF9" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG9" s="39">
+        <v>4</v>
+      </c>
+      <c r="BH9" s="39">
+        <v>1</v>
+      </c>
+      <c r="BI9" s="39">
+        <v>2</v>
+      </c>
+      <c r="BJ9" s="39">
+        <v>2</v>
+      </c>
+      <c r="BK9" s="39">
+        <v>2</v>
+      </c>
+      <c r="BL9" s="39">
+        <v>5</v>
+      </c>
+      <c r="BM9" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN9" s="39">
+        <v>4</v>
+      </c>
+      <c r="BO9" s="39">
+        <v>1</v>
+      </c>
+      <c r="BP9" s="39">
+        <v>1</v>
+      </c>
+      <c r="BQ9" s="39">
+        <v>2</v>
+      </c>
+      <c r="BR9" s="39">
+        <v>3</v>
+      </c>
+      <c r="BS9" s="39">
+        <v>5</v>
+      </c>
+      <c r="BT9" s="39">
+        <v>1</v>
+      </c>
+      <c r="BU9" s="39">
+        <v>1</v>
+      </c>
+      <c r="BV9" s="39">
+        <v>3</v>
+      </c>
+      <c r="BW9" s="39">
+        <v>4</v>
+      </c>
+      <c r="BX9" s="39">
+        <v>5</v>
+      </c>
+      <c r="BY9" s="39">
+        <v>5</v>
+      </c>
+      <c r="BZ9" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A10" s="40">
+        <v>11</v>
+      </c>
+      <c r="B10" s="39">
+        <v>5</v>
+      </c>
+      <c r="C10" s="39">
+        <v>2</v>
+      </c>
+      <c r="D10" s="39">
+        <v>3</v>
+      </c>
+      <c r="E10" s="39">
+        <v>2</v>
+      </c>
+      <c r="F10" s="39">
+        <v>2</v>
+      </c>
+      <c r="G10" s="39">
+        <v>1</v>
+      </c>
+      <c r="H10" s="39">
+        <v>2</v>
+      </c>
+      <c r="I10" s="39">
+        <v>3</v>
+      </c>
+      <c r="J10" s="39">
+        <v>2</v>
+      </c>
+      <c r="K10" s="39">
+        <v>4</v>
+      </c>
+      <c r="L10" s="39">
+        <v>2</v>
+      </c>
+      <c r="M10" s="39">
+        <v>3</v>
+      </c>
+      <c r="N10" s="39">
+        <v>3</v>
+      </c>
+      <c r="O10" s="39">
+        <v>3</v>
+      </c>
+      <c r="P10" s="39">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="39">
+        <v>5</v>
+      </c>
+      <c r="R10" s="39">
+        <v>5</v>
+      </c>
+      <c r="S10" s="39">
+        <v>5</v>
+      </c>
+      <c r="T10" s="39">
+        <v>5</v>
+      </c>
+      <c r="U10" s="39">
+        <v>5</v>
+      </c>
+      <c r="V10" s="39">
+        <v>5</v>
+      </c>
+      <c r="W10" s="39">
+        <v>1</v>
+      </c>
+      <c r="X10" s="39">
+        <v>2</v>
+      </c>
+      <c r="Y10" s="39">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="39">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="39">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="39">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="39">
+        <v>2</v>
+      </c>
+      <c r="AD10" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="39">
+        <v>3</v>
+      </c>
+      <c r="AG10" s="39">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="39">
+        <v>3</v>
+      </c>
+      <c r="AI10" s="39">
+        <v>3</v>
+      </c>
+      <c r="AJ10" s="39">
+        <v>3</v>
+      </c>
+      <c r="AK10" s="39">
+        <v>3</v>
+      </c>
+      <c r="AL10" s="39">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="39">
+        <v>2</v>
+      </c>
+      <c r="AN10" s="39">
+        <v>1</v>
+      </c>
+      <c r="AO10" s="39">
+        <v>2</v>
+      </c>
+      <c r="AP10" s="39">
+        <v>2</v>
+      </c>
+      <c r="AQ10" s="39">
+        <v>2</v>
+      </c>
+      <c r="AR10" s="39">
+        <v>2</v>
+      </c>
+      <c r="AS10" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT10" s="39">
+        <v>4</v>
+      </c>
+      <c r="AU10" s="39">
+        <v>4</v>
+      </c>
+      <c r="AV10" s="39">
+        <v>2</v>
+      </c>
+      <c r="AW10" s="39">
+        <v>2</v>
+      </c>
+      <c r="AX10" s="39">
+        <v>2</v>
+      </c>
+      <c r="AY10" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ10" s="39">
+        <v>3</v>
+      </c>
+      <c r="BA10" s="39">
+        <v>2</v>
+      </c>
+      <c r="BB10" s="39">
+        <v>1</v>
+      </c>
+      <c r="BC10" s="39">
+        <v>3</v>
+      </c>
+      <c r="BD10" s="39">
+        <v>3</v>
+      </c>
+      <c r="BE10" s="39">
+        <v>3</v>
+      </c>
+      <c r="BF10" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG10" s="39">
+        <v>3</v>
+      </c>
+      <c r="BH10" s="39">
+        <v>2</v>
+      </c>
+      <c r="BI10" s="39">
+        <v>1</v>
+      </c>
+      <c r="BJ10" s="39">
+        <v>3</v>
+      </c>
+      <c r="BK10" s="39">
+        <v>3</v>
+      </c>
+      <c r="BL10" s="39">
+        <v>3</v>
+      </c>
+      <c r="BM10" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN10" s="39">
+        <v>3</v>
+      </c>
+      <c r="BO10" s="39">
+        <v>2</v>
+      </c>
+      <c r="BP10" s="39">
+        <v>1</v>
+      </c>
+      <c r="BQ10" s="39">
+        <v>4</v>
+      </c>
+      <c r="BR10" s="39">
+        <v>4</v>
+      </c>
+      <c r="BS10" s="39">
+        <v>4</v>
+      </c>
+      <c r="BT10" s="39">
+        <v>1</v>
+      </c>
+      <c r="BU10" s="39">
+        <v>1</v>
+      </c>
+      <c r="BV10" s="39">
+        <v>4</v>
+      </c>
+      <c r="BW10" s="39">
+        <v>4</v>
+      </c>
+      <c r="BX10" s="39">
+        <v>2</v>
+      </c>
+      <c r="BY10" s="39">
+        <v>2</v>
+      </c>
+      <c r="BZ10" s="39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A11" s="40">
+        <v>12</v>
+      </c>
+      <c r="B11" s="39">
+        <v>5</v>
+      </c>
+      <c r="C11" s="39">
+        <v>3</v>
+      </c>
+      <c r="D11" s="39">
+        <v>1</v>
+      </c>
+      <c r="E11" s="39">
+        <v>3</v>
+      </c>
+      <c r="F11" s="39">
+        <v>4</v>
+      </c>
+      <c r="G11" s="39">
+        <v>4</v>
+      </c>
+      <c r="H11" s="39">
+        <v>4</v>
+      </c>
+      <c r="I11" s="39">
+        <v>5</v>
+      </c>
+      <c r="J11" s="39">
+        <v>3</v>
+      </c>
+      <c r="K11" s="39">
+        <v>4</v>
+      </c>
+      <c r="L11" s="39">
+        <v>5</v>
+      </c>
+      <c r="M11" s="39">
+        <v>4</v>
+      </c>
+      <c r="N11" s="39">
+        <v>4</v>
+      </c>
+      <c r="O11" s="39">
+        <v>4</v>
+      </c>
+      <c r="P11" s="39">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="39">
+        <v>3</v>
+      </c>
+      <c r="R11" s="39">
+        <v>2</v>
+      </c>
+      <c r="S11" s="39">
+        <v>5</v>
+      </c>
+      <c r="T11" s="39">
+        <v>2</v>
+      </c>
+      <c r="U11" s="39">
+        <v>2</v>
+      </c>
+      <c r="V11" s="39">
+        <v>2</v>
+      </c>
+      <c r="W11" s="39">
+        <v>4</v>
+      </c>
+      <c r="X11" s="39">
+        <v>3</v>
+      </c>
+      <c r="Y11" s="39">
+        <v>5</v>
+      </c>
+      <c r="Z11" s="39">
+        <v>5</v>
+      </c>
+      <c r="AA11" s="39">
+        <v>3</v>
+      </c>
+      <c r="AB11" s="39">
+        <v>3</v>
+      </c>
+      <c r="AC11" s="39">
+        <v>3</v>
+      </c>
+      <c r="AD11" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE11" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF11" s="39">
+        <v>4</v>
+      </c>
+      <c r="AG11" s="39">
+        <v>2</v>
+      </c>
+      <c r="AH11" s="39">
+        <v>3</v>
+      </c>
+      <c r="AI11" s="39">
+        <v>3</v>
+      </c>
+      <c r="AJ11" s="39">
+        <v>3</v>
+      </c>
+      <c r="AK11" s="39">
+        <v>5</v>
+      </c>
+      <c r="AL11" s="39">
+        <v>2</v>
+      </c>
+      <c r="AM11" s="39">
+        <v>2</v>
+      </c>
+      <c r="AN11" s="39">
+        <v>4</v>
+      </c>
+      <c r="AO11" s="39">
+        <v>3</v>
+      </c>
+      <c r="AP11" s="39">
+        <v>3</v>
+      </c>
+      <c r="AQ11" s="39">
+        <v>3</v>
+      </c>
+      <c r="AR11" s="39">
+        <v>4</v>
+      </c>
+      <c r="AS11" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT11" s="39">
+        <v>2</v>
+      </c>
+      <c r="AU11" s="39">
+        <v>1</v>
+      </c>
+      <c r="AV11" s="39">
+        <v>3</v>
+      </c>
+      <c r="AW11" s="39">
+        <v>3</v>
+      </c>
+      <c r="AX11" s="39">
+        <v>3</v>
+      </c>
+      <c r="AY11" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ11" s="39">
+        <v>2</v>
+      </c>
+      <c r="BA11" s="39">
+        <v>2</v>
+      </c>
+      <c r="BB11" s="39">
+        <v>4</v>
+      </c>
+      <c r="BC11" s="39">
+        <v>3</v>
+      </c>
+      <c r="BD11" s="39">
+        <v>3</v>
+      </c>
+      <c r="BE11" s="39">
+        <v>3</v>
+      </c>
+      <c r="BF11" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG11" s="39">
+        <v>2</v>
+      </c>
+      <c r="BH11" s="39">
+        <v>2</v>
+      </c>
+      <c r="BI11" s="39">
+        <v>3</v>
+      </c>
+      <c r="BJ11" s="39">
+        <v>3</v>
+      </c>
+      <c r="BK11" s="39">
+        <v>3</v>
+      </c>
+      <c r="BL11" s="39">
+        <v>3</v>
+      </c>
+      <c r="BM11" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN11" s="39">
+        <v>2</v>
+      </c>
+      <c r="BO11" s="39">
+        <v>2</v>
+      </c>
+      <c r="BP11" s="39">
+        <v>3</v>
+      </c>
+      <c r="BQ11" s="39">
+        <v>4</v>
+      </c>
+      <c r="BR11" s="39">
+        <v>4</v>
+      </c>
+      <c r="BS11" s="39">
+        <v>4</v>
+      </c>
+      <c r="BT11" s="39">
+        <v>3</v>
+      </c>
+      <c r="BU11" s="39">
+        <v>1</v>
+      </c>
+      <c r="BV11" s="39">
+        <v>1</v>
+      </c>
+      <c r="BW11" s="39">
+        <v>1</v>
+      </c>
+      <c r="BX11" s="39">
+        <v>5</v>
+      </c>
+      <c r="BY11" s="39">
+        <v>5</v>
+      </c>
+      <c r="BZ11" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A12" s="40">
+        <v>13</v>
+      </c>
+      <c r="B12" s="39">
+        <v>4</v>
+      </c>
+      <c r="C12" s="39">
+        <v>4</v>
+      </c>
+      <c r="D12" s="39">
+        <v>2</v>
+      </c>
+      <c r="E12" s="39">
+        <v>3</v>
+      </c>
+      <c r="F12" s="39">
+        <v>4</v>
+      </c>
+      <c r="G12" s="39">
+        <v>4</v>
+      </c>
+      <c r="H12" s="39">
+        <v>4</v>
+      </c>
+      <c r="I12" s="39">
+        <v>4</v>
+      </c>
+      <c r="J12" s="39">
+        <v>1</v>
+      </c>
+      <c r="K12" s="39">
+        <v>4</v>
+      </c>
+      <c r="L12" s="39">
+        <v>2</v>
+      </c>
+      <c r="M12" s="39">
+        <v>3</v>
+      </c>
+      <c r="N12" s="39">
+        <v>3</v>
+      </c>
+      <c r="O12" s="39">
+        <v>3</v>
+      </c>
+      <c r="P12" s="39">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="39">
+        <v>2</v>
+      </c>
+      <c r="R12" s="39">
+        <v>2</v>
+      </c>
+      <c r="S12" s="39">
+        <v>2</v>
+      </c>
+      <c r="T12" s="39">
+        <v>1</v>
+      </c>
+      <c r="U12" s="39">
+        <v>2</v>
+      </c>
+      <c r="V12" s="39">
+        <v>2</v>
+      </c>
+      <c r="W12" s="39">
+        <v>2</v>
+      </c>
+      <c r="X12" s="39">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="39">
+        <v>5</v>
+      </c>
+      <c r="Z12" s="39">
+        <v>4</v>
+      </c>
+      <c r="AA12" s="39">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="39">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="39">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="39">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF12" s="39">
+        <v>2</v>
+      </c>
+      <c r="AG12" s="39">
+        <v>3</v>
+      </c>
+      <c r="AH12" s="39">
+        <v>5</v>
+      </c>
+      <c r="AI12" s="39">
+        <v>4</v>
+      </c>
+      <c r="AJ12" s="39">
+        <v>2</v>
+      </c>
+      <c r="AK12" s="39">
+        <v>1</v>
+      </c>
+      <c r="AL12" s="39">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="39">
+        <v>1</v>
+      </c>
+      <c r="AN12" s="39">
+        <v>1</v>
+      </c>
+      <c r="AO12" s="39">
+        <v>5</v>
+      </c>
+      <c r="AP12" s="39">
+        <v>1</v>
+      </c>
+      <c r="AQ12" s="39">
+        <v>1</v>
+      </c>
+      <c r="AR12" s="39">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT12" s="39">
+        <v>1</v>
+      </c>
+      <c r="AU12" s="39">
+        <v>1</v>
+      </c>
+      <c r="AV12" s="39">
+        <v>3</v>
+      </c>
+      <c r="AW12" s="39">
+        <v>3</v>
+      </c>
+      <c r="AX12" s="39">
+        <v>3</v>
+      </c>
+      <c r="AY12" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ12" s="39">
+        <v>3</v>
+      </c>
+      <c r="BA12" s="39">
+        <v>4</v>
+      </c>
+      <c r="BB12" s="39">
+        <v>4</v>
+      </c>
+      <c r="BC12" s="39">
+        <v>4</v>
+      </c>
+      <c r="BD12" s="39">
+        <v>4</v>
+      </c>
+      <c r="BE12" s="39">
+        <v>4</v>
+      </c>
+      <c r="BF12" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG12" s="39">
+        <v>4</v>
+      </c>
+      <c r="BH12" s="39">
+        <v>3</v>
+      </c>
+      <c r="BI12" s="39">
+        <v>3</v>
+      </c>
+      <c r="BJ12" s="39">
+        <v>2</v>
+      </c>
+      <c r="BK12" s="39">
+        <v>4</v>
+      </c>
+      <c r="BL12" s="39">
+        <v>4</v>
+      </c>
+      <c r="BM12" s="39">
+        <v>4</v>
+      </c>
+      <c r="BN12" s="39">
+        <v>5</v>
+      </c>
+      <c r="BO12" s="39">
+        <v>3</v>
+      </c>
+      <c r="BP12" s="39">
+        <v>3</v>
+      </c>
+      <c r="BQ12" s="39">
+        <v>1</v>
+      </c>
+      <c r="BR12" s="39">
+        <v>5</v>
+      </c>
+      <c r="BS12" s="39">
+        <v>5</v>
+      </c>
+      <c r="BT12" s="39">
+        <v>5</v>
+      </c>
+      <c r="BU12" s="39">
+        <v>1</v>
+      </c>
+      <c r="BV12" s="39">
+        <v>5</v>
+      </c>
+      <c r="BW12" s="39">
+        <v>5</v>
+      </c>
+      <c r="BX12" s="39">
+        <v>5</v>
+      </c>
+      <c r="BY12" s="39">
+        <v>5</v>
+      </c>
+      <c r="BZ12" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A13" s="40">
+        <v>14</v>
+      </c>
+      <c r="B13" s="39">
+        <v>5</v>
+      </c>
+      <c r="C13" s="39">
+        <v>5</v>
+      </c>
+      <c r="D13" s="39">
+        <v>2</v>
+      </c>
+      <c r="E13" s="39">
+        <v>5</v>
+      </c>
+      <c r="F13" s="39">
+        <v>3</v>
+      </c>
+      <c r="G13" s="39">
+        <v>3</v>
+      </c>
+      <c r="H13" s="39">
+        <v>4</v>
+      </c>
+      <c r="I13" s="39">
+        <v>4</v>
+      </c>
+      <c r="J13" s="39">
+        <v>5</v>
+      </c>
+      <c r="K13" s="39">
+        <v>4</v>
+      </c>
+      <c r="L13" s="39">
+        <v>5</v>
+      </c>
+      <c r="M13" s="39">
+        <v>4</v>
+      </c>
+      <c r="N13" s="39">
+        <v>4</v>
+      </c>
+      <c r="O13" s="39">
+        <v>4</v>
+      </c>
+      <c r="P13" s="39">
+        <v>4</v>
+      </c>
+      <c r="Q13" s="39">
+        <v>3</v>
+      </c>
+      <c r="R13" s="39">
+        <v>1</v>
+      </c>
+      <c r="S13" s="39">
+        <v>5</v>
+      </c>
+      <c r="T13" s="39">
+        <v>3</v>
+      </c>
+      <c r="U13" s="39">
+        <v>3</v>
+      </c>
+      <c r="V13" s="39">
+        <v>4</v>
+      </c>
+      <c r="W13" s="39">
+        <v>2</v>
+      </c>
+      <c r="X13" s="39">
+        <v>5</v>
+      </c>
+      <c r="Y13" s="39">
+        <v>5</v>
+      </c>
+      <c r="Z13" s="39">
+        <v>5</v>
+      </c>
+      <c r="AA13" s="39">
+        <v>2</v>
+      </c>
+      <c r="AB13" s="39">
+        <v>2</v>
+      </c>
+      <c r="AC13" s="39">
+        <v>2</v>
+      </c>
+      <c r="AD13" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE13" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF13" s="39">
+        <v>5</v>
+      </c>
+      <c r="AG13" s="39">
+        <v>4</v>
+      </c>
+      <c r="AH13" s="39">
+        <v>3</v>
+      </c>
+      <c r="AI13" s="39">
+        <v>2</v>
+      </c>
+      <c r="AJ13" s="39">
+        <v>4</v>
+      </c>
+      <c r="AK13" s="39">
+        <v>4</v>
+      </c>
+      <c r="AL13" s="39">
+        <v>5</v>
+      </c>
+      <c r="AM13" s="39">
+        <v>4</v>
+      </c>
+      <c r="AN13" s="39">
+        <v>5</v>
+      </c>
+      <c r="AO13" s="39">
+        <v>3</v>
+      </c>
+      <c r="AP13" s="39">
+        <v>3</v>
+      </c>
+      <c r="AQ13" s="39">
+        <v>4</v>
+      </c>
+      <c r="AR13" s="39">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT13" s="39">
+        <v>3</v>
+      </c>
+      <c r="AU13" s="39">
+        <v>3</v>
+      </c>
+      <c r="AV13" s="39">
+        <v>1</v>
+      </c>
+      <c r="AW13" s="39">
+        <v>1</v>
+      </c>
+      <c r="AX13" s="39">
+        <v>1</v>
+      </c>
+      <c r="AY13" s="39">
+        <v>4</v>
+      </c>
+      <c r="AZ13" s="39">
+        <v>4</v>
+      </c>
+      <c r="BA13" s="39">
+        <v>1</v>
+      </c>
+      <c r="BB13" s="39">
+        <v>5</v>
+      </c>
+      <c r="BC13" s="39">
+        <v>3</v>
+      </c>
+      <c r="BD13" s="39">
+        <v>3</v>
+      </c>
+      <c r="BE13" s="39">
+        <v>3</v>
+      </c>
+      <c r="BF13" s="39">
+        <v>4</v>
+      </c>
+      <c r="BG13" s="39">
+        <v>3</v>
+      </c>
+      <c r="BH13" s="39">
+        <v>1</v>
+      </c>
+      <c r="BI13" s="39">
+        <v>3</v>
+      </c>
+      <c r="BJ13" s="39">
+        <v>2</v>
+      </c>
+      <c r="BK13" s="39">
+        <v>3</v>
+      </c>
+      <c r="BL13" s="39">
+        <v>4</v>
+      </c>
+      <c r="BM13" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN13" s="39">
+        <v>4</v>
+      </c>
+      <c r="BO13" s="39">
+        <v>1</v>
+      </c>
+      <c r="BP13" s="39">
+        <v>1</v>
+      </c>
+      <c r="BQ13" s="39">
+        <v>2</v>
+      </c>
+      <c r="BR13" s="39">
+        <v>3</v>
+      </c>
+      <c r="BS13" s="39">
+        <v>4</v>
+      </c>
+      <c r="BT13" s="39">
+        <v>4</v>
+      </c>
+      <c r="BU13" s="39">
+        <v>3</v>
+      </c>
+      <c r="BV13" s="39">
+        <v>2</v>
+      </c>
+      <c r="BW13" s="39">
+        <v>3</v>
+      </c>
+      <c r="BX13" s="39">
+        <v>3</v>
+      </c>
+      <c r="BY13" s="39">
+        <v>4</v>
+      </c>
+      <c r="BZ13" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A14" s="40">
+        <v>15</v>
+      </c>
+      <c r="B14" s="39">
+        <v>4</v>
+      </c>
+      <c r="C14" s="39">
+        <v>2</v>
+      </c>
+      <c r="D14" s="39">
+        <v>4</v>
+      </c>
+      <c r="E14" s="39">
+        <v>3</v>
+      </c>
+      <c r="F14" s="39">
+        <v>4</v>
+      </c>
+      <c r="G14" s="39">
+        <v>4</v>
+      </c>
+      <c r="H14" s="39">
+        <v>4</v>
+      </c>
+      <c r="I14" s="39">
+        <v>2</v>
+      </c>
+      <c r="J14" s="39">
+        <v>3</v>
+      </c>
+      <c r="K14" s="39">
+        <v>5</v>
+      </c>
+      <c r="L14" s="39">
+        <v>4</v>
+      </c>
+      <c r="M14" s="39">
+        <v>3</v>
+      </c>
+      <c r="N14" s="39">
+        <v>3</v>
+      </c>
+      <c r="O14" s="39">
+        <v>3</v>
+      </c>
+      <c r="P14" s="39">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="39">
+        <v>3</v>
+      </c>
+      <c r="R14" s="39">
+        <v>4</v>
+      </c>
+      <c r="S14" s="39">
+        <v>3</v>
+      </c>
+      <c r="T14" s="39">
+        <v>4</v>
+      </c>
+      <c r="U14" s="39">
+        <v>4</v>
+      </c>
+      <c r="V14" s="39">
+        <v>4</v>
+      </c>
+      <c r="W14" s="39">
+        <v>3</v>
+      </c>
+      <c r="X14" s="39">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="39">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="39">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="39">
+        <v>3</v>
+      </c>
+      <c r="AB14" s="39">
+        <v>3</v>
+      </c>
+      <c r="AC14" s="39">
+        <v>4</v>
+      </c>
+      <c r="AD14" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE14" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF14" s="39">
+        <v>4</v>
+      </c>
+      <c r="AG14" s="39">
+        <v>3</v>
+      </c>
+      <c r="AH14" s="39">
+        <v>4</v>
+      </c>
+      <c r="AI14" s="39">
+        <v>4</v>
+      </c>
+      <c r="AJ14" s="39">
+        <v>4</v>
+      </c>
+      <c r="AK14" s="39">
+        <v>3</v>
+      </c>
+      <c r="AL14" s="39">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="39">
+        <v>5</v>
+      </c>
+      <c r="AN14" s="39">
+        <v>3</v>
+      </c>
+      <c r="AO14" s="39">
+        <v>4</v>
+      </c>
+      <c r="AP14" s="39">
+        <v>4</v>
+      </c>
+      <c r="AQ14" s="39">
+        <v>4</v>
+      </c>
+      <c r="AR14" s="39">
+        <v>3</v>
+      </c>
+      <c r="AS14" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT14" s="39">
+        <v>4</v>
+      </c>
+      <c r="AU14" s="39">
+        <v>4</v>
+      </c>
+      <c r="AV14" s="39">
+        <v>3</v>
+      </c>
+      <c r="AW14" s="39">
+        <v>3</v>
+      </c>
+      <c r="AX14" s="39">
+        <v>3</v>
+      </c>
+      <c r="AY14" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ14" s="39">
+        <v>3</v>
+      </c>
+      <c r="BA14" s="39">
+        <v>5</v>
+      </c>
+      <c r="BB14" s="39">
+        <v>3</v>
+      </c>
+      <c r="BC14" s="39">
+        <v>5</v>
+      </c>
+      <c r="BD14" s="39">
+        <v>5</v>
+      </c>
+      <c r="BE14" s="39">
+        <v>5</v>
+      </c>
+      <c r="BF14" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG14" s="39">
+        <v>4</v>
+      </c>
+      <c r="BH14" s="39">
+        <v>4</v>
+      </c>
+      <c r="BI14" s="39">
+        <v>2</v>
+      </c>
+      <c r="BJ14" s="39">
+        <v>5</v>
+      </c>
+      <c r="BK14" s="39">
+        <v>5</v>
+      </c>
+      <c r="BL14" s="39">
+        <v>5</v>
+      </c>
+      <c r="BM14" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN14" s="39">
+        <v>3</v>
+      </c>
+      <c r="BO14" s="39">
+        <v>4</v>
+      </c>
+      <c r="BP14" s="39">
+        <v>3</v>
+      </c>
+      <c r="BQ14" s="39">
+        <v>4</v>
+      </c>
+      <c r="BR14" s="39">
+        <v>4</v>
+      </c>
+      <c r="BS14" s="39">
+        <v>4</v>
+      </c>
+      <c r="BT14" s="39">
+        <v>4</v>
+      </c>
+      <c r="BU14" s="39">
+        <v>3</v>
+      </c>
+      <c r="BV14" s="39">
+        <v>5</v>
+      </c>
+      <c r="BW14" s="39">
+        <v>4</v>
+      </c>
+      <c r="BX14" s="39">
+        <v>5</v>
+      </c>
+      <c r="BY14" s="39">
+        <v>5</v>
+      </c>
+      <c r="BZ14" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A15" s="40">
+        <v>16</v>
+      </c>
+      <c r="B15" s="39">
+        <v>4</v>
+      </c>
+      <c r="C15" s="39">
+        <v>4</v>
+      </c>
+      <c r="D15" s="39">
+        <v>3</v>
+      </c>
+      <c r="E15" s="39">
+        <v>3</v>
+      </c>
+      <c r="F15" s="39">
+        <v>4</v>
+      </c>
+      <c r="G15" s="39">
+        <v>4</v>
+      </c>
+      <c r="H15" s="39">
+        <v>4</v>
+      </c>
+      <c r="I15" s="39">
+        <v>3</v>
+      </c>
+      <c r="J15" s="39">
+        <v>3</v>
+      </c>
+      <c r="K15" s="39">
+        <v>5</v>
+      </c>
+      <c r="L15" s="39">
+        <v>4</v>
+      </c>
+      <c r="M15" s="39">
+        <v>4</v>
+      </c>
+      <c r="N15" s="39">
+        <v>4</v>
+      </c>
+      <c r="O15" s="39">
+        <v>3</v>
+      </c>
+      <c r="P15" s="39">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="39">
+        <v>4</v>
+      </c>
+      <c r="R15" s="39">
+        <v>4</v>
+      </c>
+      <c r="S15" s="39">
+        <v>4</v>
+      </c>
+      <c r="T15" s="39">
+        <v>4</v>
+      </c>
+      <c r="U15" s="39">
+        <v>4</v>
+      </c>
+      <c r="V15" s="39">
+        <v>3</v>
+      </c>
+      <c r="W15" s="39">
+        <v>4</v>
+      </c>
+      <c r="X15" s="39">
+        <v>4</v>
+      </c>
+      <c r="Y15" s="39">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="39">
+        <v>5</v>
+      </c>
+      <c r="AA15" s="39">
+        <v>4</v>
+      </c>
+      <c r="AB15" s="39">
+        <v>4</v>
+      </c>
+      <c r="AC15" s="39">
+        <v>4</v>
+      </c>
+      <c r="AD15" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE15" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF15" s="39">
+        <v>4</v>
+      </c>
+      <c r="AG15" s="39">
+        <v>3</v>
+      </c>
+      <c r="AH15" s="39">
+        <v>5</v>
+      </c>
+      <c r="AI15" s="39">
+        <v>5</v>
+      </c>
+      <c r="AJ15" s="39">
+        <v>5</v>
+      </c>
+      <c r="AK15" s="39">
+        <v>3</v>
+      </c>
+      <c r="AL15" s="39">
+        <v>4</v>
+      </c>
+      <c r="AM15" s="39">
+        <v>3</v>
+      </c>
+      <c r="AN15" s="39">
+        <v>4</v>
+      </c>
+      <c r="AO15" s="39">
+        <v>5</v>
+      </c>
+      <c r="AP15" s="39">
+        <v>5</v>
+      </c>
+      <c r="AQ15" s="39">
+        <v>5</v>
+      </c>
+      <c r="AR15" s="39">
+        <v>3</v>
+      </c>
+      <c r="AS15" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT15" s="39">
+        <v>3</v>
+      </c>
+      <c r="AU15" s="39">
+        <v>3</v>
+      </c>
+      <c r="AV15" s="39">
+        <v>3</v>
+      </c>
+      <c r="AW15" s="39">
+        <v>3</v>
+      </c>
+      <c r="AX15" s="39">
+        <v>3</v>
+      </c>
+      <c r="AY15" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ15" s="39">
+        <v>3</v>
+      </c>
+      <c r="BA15" s="39">
+        <v>4</v>
+      </c>
+      <c r="BB15" s="39">
+        <v>4</v>
+      </c>
+      <c r="BC15" s="39">
+        <v>4</v>
+      </c>
+      <c r="BD15" s="39">
+        <v>4</v>
+      </c>
+      <c r="BE15" s="39">
+        <v>4</v>
+      </c>
+      <c r="BF15" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG15" s="39">
+        <v>3</v>
+      </c>
+      <c r="BH15" s="39">
+        <v>3</v>
+      </c>
+      <c r="BI15" s="39">
+        <v>4</v>
+      </c>
+      <c r="BJ15" s="39">
+        <v>5</v>
+      </c>
+      <c r="BK15" s="39">
+        <v>4</v>
+      </c>
+      <c r="BL15" s="39">
+        <v>4</v>
+      </c>
+      <c r="BM15" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN15" s="39">
+        <v>2</v>
+      </c>
+      <c r="BO15" s="39">
+        <v>2</v>
+      </c>
+      <c r="BP15" s="39">
+        <v>2</v>
+      </c>
+      <c r="BQ15" s="39">
+        <v>4</v>
+      </c>
+      <c r="BR15" s="39">
+        <v>4</v>
+      </c>
+      <c r="BS15" s="39">
+        <v>4</v>
+      </c>
+      <c r="BT15" s="39">
+        <v>3</v>
+      </c>
+      <c r="BU15" s="39">
+        <v>3</v>
+      </c>
+      <c r="BV15" s="39">
+        <v>3</v>
+      </c>
+      <c r="BW15" s="39">
+        <v>3</v>
+      </c>
+      <c r="BX15" s="39">
+        <v>5</v>
+      </c>
+      <c r="BY15" s="39">
+        <v>5</v>
+      </c>
+      <c r="BZ15" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A16" s="40">
+        <v>17</v>
+      </c>
+      <c r="B16" s="39">
+        <v>5</v>
+      </c>
+      <c r="C16" s="39">
+        <v>4</v>
+      </c>
+      <c r="D16" s="39">
+        <v>4</v>
+      </c>
+      <c r="E16" s="39">
+        <v>3</v>
+      </c>
+      <c r="F16" s="39">
+        <v>3</v>
+      </c>
+      <c r="G16" s="39">
+        <v>3</v>
+      </c>
+      <c r="H16" s="39">
+        <v>1</v>
+      </c>
+      <c r="I16" s="39">
+        <v>5</v>
+      </c>
+      <c r="J16" s="39">
+        <v>5</v>
+      </c>
+      <c r="K16" s="39">
+        <v>5</v>
+      </c>
+      <c r="L16" s="39">
+        <v>5</v>
+      </c>
+      <c r="M16" s="39">
+        <v>3</v>
+      </c>
+      <c r="N16" s="39">
+        <v>3</v>
+      </c>
+      <c r="O16" s="39">
+        <v>3</v>
+      </c>
+      <c r="P16" s="39">
+        <v>4</v>
+      </c>
+      <c r="Q16" s="39">
+        <v>4</v>
+      </c>
+      <c r="R16" s="39">
+        <v>3</v>
+      </c>
+      <c r="S16" s="39">
+        <v>3</v>
+      </c>
+      <c r="T16" s="39">
+        <v>4</v>
+      </c>
+      <c r="U16" s="39">
+        <v>4</v>
+      </c>
+      <c r="V16" s="39">
+        <v>3</v>
+      </c>
+      <c r="W16" s="39">
+        <v>4</v>
+      </c>
+      <c r="X16" s="39">
+        <v>4</v>
+      </c>
+      <c r="Y16" s="39">
+        <v>5</v>
+      </c>
+      <c r="Z16" s="39">
+        <v>5</v>
+      </c>
+      <c r="AA16" s="39">
+        <v>3</v>
+      </c>
+      <c r="AB16" s="39">
+        <v>3</v>
+      </c>
+      <c r="AC16" s="39">
+        <v>3</v>
+      </c>
+      <c r="AD16" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE16" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF16" s="39">
+        <v>5</v>
+      </c>
+      <c r="AG16" s="39">
+        <v>3</v>
+      </c>
+      <c r="AH16" s="39">
+        <v>4</v>
+      </c>
+      <c r="AI16" s="39">
+        <v>4</v>
+      </c>
+      <c r="AJ16" s="39">
+        <v>2</v>
+      </c>
+      <c r="AK16" s="39">
+        <v>4</v>
+      </c>
+      <c r="AL16" s="39">
+        <v>4</v>
+      </c>
+      <c r="AM16" s="39">
+        <v>5</v>
+      </c>
+      <c r="AN16" s="39">
+        <v>4</v>
+      </c>
+      <c r="AO16" s="39">
+        <v>3</v>
+      </c>
+      <c r="AP16" s="39">
+        <v>4</v>
+      </c>
+      <c r="AQ16" s="39">
+        <v>4</v>
+      </c>
+      <c r="AR16" s="39">
+        <v>5</v>
+      </c>
+      <c r="AS16" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT16" s="39">
+        <v>5</v>
+      </c>
+      <c r="AU16" s="39">
+        <v>3</v>
+      </c>
+      <c r="AV16" s="39">
+        <v>4</v>
+      </c>
+      <c r="AW16" s="39">
+        <v>4</v>
+      </c>
+      <c r="AX16" s="39">
+        <v>4</v>
+      </c>
+      <c r="AY16" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ16" s="39">
+        <v>5</v>
+      </c>
+      <c r="BA16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BB16" s="39">
+        <v>3</v>
+      </c>
+      <c r="BC16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BD16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BE16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BF16" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG16" s="39">
+        <v>5</v>
+      </c>
+      <c r="BH16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BI16" s="39">
+        <v>3</v>
+      </c>
+      <c r="BJ16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BK16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BL16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BM16" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN16" s="39">
+        <v>5</v>
+      </c>
+      <c r="BO16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BP16" s="39">
+        <v>3</v>
+      </c>
+      <c r="BQ16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BR16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BS16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BT16" s="39">
+        <v>1</v>
+      </c>
+      <c r="BU16" s="39">
+        <v>1</v>
+      </c>
+      <c r="BV16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BW16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BX16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BY16" s="39">
+        <v>4</v>
+      </c>
+      <c r="BZ16" s="39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A17" s="40">
+        <v>18</v>
+      </c>
+      <c r="B17" s="39">
+        <v>4</v>
+      </c>
+      <c r="C17" s="39">
+        <v>5</v>
+      </c>
+      <c r="D17" s="39">
+        <v>5</v>
+      </c>
+      <c r="E17" s="39">
+        <v>4</v>
+      </c>
+      <c r="F17" s="39">
+        <v>3</v>
+      </c>
+      <c r="G17" s="39">
+        <v>3</v>
+      </c>
+      <c r="H17" s="39">
+        <v>3</v>
+      </c>
+      <c r="I17" s="39">
+        <v>5</v>
+      </c>
+      <c r="J17" s="39">
+        <v>4</v>
+      </c>
+      <c r="K17" s="39">
+        <v>5</v>
+      </c>
+      <c r="L17" s="39">
+        <v>5</v>
+      </c>
+      <c r="M17" s="39">
+        <v>3</v>
+      </c>
+      <c r="N17" s="39">
+        <v>3</v>
+      </c>
+      <c r="O17" s="39">
+        <v>2</v>
+      </c>
+      <c r="P17" s="39">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="39">
+        <v>5</v>
+      </c>
+      <c r="R17" s="39">
+        <v>5</v>
+      </c>
+      <c r="S17" s="39">
+        <v>5</v>
+      </c>
+      <c r="T17" s="39">
+        <v>2</v>
+      </c>
+      <c r="U17" s="39">
+        <v>2</v>
+      </c>
+      <c r="V17" s="39">
+        <v>2</v>
+      </c>
+      <c r="W17" s="39">
+        <v>3</v>
+      </c>
+      <c r="X17" s="39">
+        <v>4</v>
+      </c>
+      <c r="Y17" s="39">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="39">
+        <v>5</v>
+      </c>
+      <c r="AA17" s="39">
+        <v>2</v>
+      </c>
+      <c r="AB17" s="39">
+        <v>2</v>
+      </c>
+      <c r="AC17" s="39">
+        <v>2</v>
+      </c>
+      <c r="AD17" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF17" s="39">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="39">
+        <v>4</v>
+      </c>
+      <c r="AH17" s="39">
+        <v>4</v>
+      </c>
+      <c r="AI17" s="39">
+        <v>4</v>
+      </c>
+      <c r="AJ17" s="39">
+        <v>4</v>
+      </c>
+      <c r="AK17" s="39">
+        <v>4</v>
+      </c>
+      <c r="AL17" s="39">
+        <v>4</v>
+      </c>
+      <c r="AM17" s="39">
+        <v>5</v>
+      </c>
+      <c r="AN17" s="39">
+        <v>4</v>
+      </c>
+      <c r="AO17" s="39">
+        <v>2</v>
+      </c>
+      <c r="AP17" s="39">
+        <v>2</v>
+      </c>
+      <c r="AQ17" s="39">
+        <v>2</v>
+      </c>
+      <c r="AR17" s="39">
+        <v>2</v>
+      </c>
+      <c r="AS17" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT17" s="39">
+        <v>4</v>
+      </c>
+      <c r="AU17" s="39">
+        <v>4</v>
+      </c>
+      <c r="AV17" s="39">
+        <v>2</v>
+      </c>
+      <c r="AW17" s="39">
+        <v>2</v>
+      </c>
+      <c r="AX17" s="39">
+        <v>2</v>
+      </c>
+      <c r="AY17" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ17" s="39">
+        <v>5</v>
+      </c>
+      <c r="BA17" s="39">
+        <v>5</v>
+      </c>
+      <c r="BB17" s="39">
+        <v>3</v>
+      </c>
+      <c r="BC17" s="39">
+        <v>3</v>
+      </c>
+      <c r="BD17" s="39">
+        <v>3</v>
+      </c>
+      <c r="BE17" s="39">
+        <v>2</v>
+      </c>
+      <c r="BF17" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG17" s="39">
+        <v>5</v>
+      </c>
+      <c r="BH17" s="39">
+        <v>5</v>
+      </c>
+      <c r="BI17" s="39">
+        <v>2</v>
+      </c>
+      <c r="BJ17" s="39">
+        <v>3</v>
+      </c>
+      <c r="BK17" s="39">
+        <v>3</v>
+      </c>
+      <c r="BL17" s="39">
+        <v>3</v>
+      </c>
+      <c r="BM17" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN17" s="39">
+        <v>5</v>
+      </c>
+      <c r="BO17" s="39">
+        <v>5</v>
+      </c>
+      <c r="BP17" s="39">
+        <v>2</v>
+      </c>
+      <c r="BQ17" s="39">
+        <v>3</v>
+      </c>
+      <c r="BR17" s="39">
+        <v>3</v>
+      </c>
+      <c r="BS17" s="39">
+        <v>3</v>
+      </c>
+      <c r="BT17" s="39">
+        <v>2</v>
+      </c>
+      <c r="BU17" s="39">
+        <v>3</v>
+      </c>
+      <c r="BV17" s="39">
+        <v>4</v>
+      </c>
+      <c r="BW17" s="39">
+        <v>5</v>
+      </c>
+      <c r="BX17" s="39">
+        <v>4</v>
+      </c>
+      <c r="BY17" s="39">
+        <v>4</v>
+      </c>
+      <c r="BZ17" s="39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A18" s="40">
+        <v>20</v>
+      </c>
+      <c r="B18" s="39">
+        <v>4</v>
+      </c>
+      <c r="C18" s="39">
+        <v>2</v>
+      </c>
+      <c r="D18" s="39">
+        <v>2</v>
+      </c>
+      <c r="E18" s="39">
+        <v>3</v>
+      </c>
+      <c r="F18" s="39">
+        <v>3</v>
+      </c>
+      <c r="G18" s="39">
+        <v>3</v>
+      </c>
+      <c r="H18" s="39">
+        <v>3</v>
+      </c>
+      <c r="I18" s="39">
+        <v>2</v>
+      </c>
+      <c r="J18" s="39">
+        <v>3</v>
+      </c>
+      <c r="K18" s="39">
+        <v>4</v>
+      </c>
+      <c r="L18" s="39">
+        <v>3</v>
+      </c>
+      <c r="M18" s="39">
+        <v>3</v>
+      </c>
+      <c r="N18" s="39">
+        <v>3</v>
+      </c>
+      <c r="O18" s="39">
+        <v>3</v>
+      </c>
+      <c r="P18" s="39">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="39">
+        <v>1</v>
+      </c>
+      <c r="R18" s="39">
+        <v>1</v>
+      </c>
+      <c r="S18" s="39">
+        <v>1</v>
+      </c>
+      <c r="T18" s="39">
+        <v>1</v>
+      </c>
+      <c r="U18" s="39">
+        <v>1</v>
+      </c>
+      <c r="V18" s="39">
+        <v>1</v>
+      </c>
+      <c r="W18" s="39">
+        <v>2</v>
+      </c>
+      <c r="X18" s="39">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="39">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="39">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="39">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="39">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="39">
+        <v>3</v>
+      </c>
+      <c r="AD18" s="39">
+        <v>2</v>
+      </c>
+      <c r="AE18" s="39">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="39">
+        <v>4</v>
+      </c>
+      <c r="AG18" s="39">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="39">
+        <v>4</v>
+      </c>
+      <c r="AI18" s="39">
+        <v>4</v>
+      </c>
+      <c r="AJ18" s="39">
+        <v>4</v>
+      </c>
+      <c r="AK18" s="39">
+        <v>4</v>
+      </c>
+      <c r="AL18" s="39">
+        <v>4</v>
+      </c>
+      <c r="AM18" s="39">
+        <v>1</v>
+      </c>
+      <c r="AN18" s="39">
+        <v>1</v>
+      </c>
+      <c r="AO18" s="39">
+        <v>1</v>
+      </c>
+      <c r="AP18" s="39">
+        <v>1</v>
+      </c>
+      <c r="AQ18" s="39">
+        <v>1</v>
+      </c>
+      <c r="AR18" s="39">
+        <v>1</v>
+      </c>
+      <c r="AS18" s="39">
+        <v>1</v>
+      </c>
+      <c r="AT18" s="39">
+        <v>1</v>
+      </c>
+      <c r="AU18" s="39">
+        <v>1</v>
+      </c>
+      <c r="AV18" s="39">
+        <v>1</v>
+      </c>
+      <c r="AW18" s="39">
+        <v>1</v>
+      </c>
+      <c r="AX18" s="39">
+        <v>1</v>
+      </c>
+      <c r="AY18" s="39">
+        <v>3</v>
+      </c>
+      <c r="AZ18" s="39">
+        <v>2</v>
+      </c>
+      <c r="BA18" s="39">
+        <v>2</v>
+      </c>
+      <c r="BB18" s="39">
+        <v>2</v>
+      </c>
+      <c r="BC18" s="39">
+        <v>2</v>
+      </c>
+      <c r="BD18" s="39">
+        <v>2</v>
+      </c>
+      <c r="BE18" s="39">
+        <v>2</v>
+      </c>
+      <c r="BF18" s="39">
+        <v>3</v>
+      </c>
+      <c r="BG18" s="39">
+        <v>2</v>
+      </c>
+      <c r="BH18" s="39">
+        <v>1</v>
+      </c>
+      <c r="BI18" s="39">
+        <v>2</v>
+      </c>
+      <c r="BJ18" s="39">
+        <v>1</v>
+      </c>
+      <c r="BK18" s="39">
+        <v>1</v>
+      </c>
+      <c r="BL18" s="39">
+        <v>1</v>
+      </c>
+      <c r="BM18" s="39">
+        <v>4</v>
+      </c>
+      <c r="BN18" s="39">
+        <v>2</v>
+      </c>
+      <c r="BO18" s="39">
+        <v>2</v>
+      </c>
+      <c r="BP18" s="39">
+        <v>2</v>
+      </c>
+      <c r="BQ18" s="39">
+        <v>2</v>
+      </c>
+      <c r="BR18" s="39">
+        <v>2</v>
+      </c>
+      <c r="BS18" s="39">
+        <v>2</v>
+      </c>
+      <c r="BT18" s="39">
+        <v>4</v>
+      </c>
+      <c r="BU18" s="39">
+        <v>2</v>
+      </c>
+      <c r="BV18" s="39">
+        <v>3</v>
+      </c>
+      <c r="BW18" s="39">
+        <v>3</v>
+      </c>
+      <c r="BX18" s="39">
+        <v>4</v>
+      </c>
+      <c r="BY18" s="39">
+        <v>4</v>
+      </c>
+      <c r="BZ18" s="39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A19" s="40">
+        <v>21</v>
+      </c>
+      <c r="B19" s="39">
+        <v>5</v>
+      </c>
+      <c r="C19" s="39">
+        <v>2</v>
+      </c>
+      <c r="D19" s="39">
+        <v>3</v>
+      </c>
+      <c r="E19" s="39">
+        <v>4</v>
+      </c>
+      <c r="F19" s="39">
+        <v>4</v>
+      </c>
+      <c r="G19" s="39">
+        <v>4</v>
+      </c>
+      <c r="H19" s="39">
+        <v>3</v>
+      </c>
+      <c r="I19" s="39">
+        <v>4</v>
+      </c>
+      <c r="J19" s="39">
+        <v>3</v>
+      </c>
+      <c r="K19" s="39">
+        <v>4</v>
+      </c>
+      <c r="L19" s="39">
+        <v>4</v>
+      </c>
+      <c r="M19" s="39">
+        <v>3</v>
+      </c>
+      <c r="N19" s="39">
+        <v>4</v>
+      </c>
+      <c r="O19" s="39">
+        <v>4</v>
+      </c>
+      <c r="P19" s="39">
+        <v>4</v>
+      </c>
+      <c r="Q19" s="39">
+        <v>2</v>
+      </c>
+      <c r="R19" s="39">
+        <v>4</v>
+      </c>
+      <c r="S19" s="39">
+        <v>3</v>
+      </c>
+      <c r="T19" s="39">
+        <v>4</v>
+      </c>
+      <c r="U19" s="39">
+        <v>3</v>
+      </c>
+      <c r="V19" s="39">
+        <v>4</v>
+      </c>
+      <c r="W19" s="39">
+        <v>4</v>
+      </c>
+      <c r="X19" s="39">
+        <v>4</v>
+      </c>
+      <c r="Y19" s="39">
+        <v>4</v>
+      </c>
+      <c r="Z19" s="39">
+        <v>4</v>
+      </c>
+      <c r="AA19" s="39">
+        <v>4</v>
+      </c>
+      <c r="AB19" s="39">
+        <v>4</v>
+      </c>
+      <c r="AC19" s="39">
+        <v>4</v>
+      </c>
+      <c r="AD19" s="39">
+        <v>3</v>
+      </c>
+      <c r="AE19" s="39">
+        <v>4</v>
+      </c>
+      <c r="AF19" s="39">
+        <v>3</v>
+      </c>
+      <c r="AG19" s="39">
+        <v>4</v>
+      </c>
+      <c r="AH19" s="39">
+        <v>4</v>
+      </c>
+      <c r="AI19" s="39">
+        <v>4</v>
+      </c>
+      <c r="AJ19" s="39">
+        <v>3</v>
+      </c>
+      <c r="AK19" s="39">
+        <v>5</v>
+      </c>
+      <c r="AL19" s="39">
+        <v>4</v>
+      </c>
+      <c r="AM19" s="39">
+        <v>3</v>
+      </c>
+      <c r="AN19" s="39">
+        <v>3</v>
+      </c>
+      <c r="AO19" s="39">
+        <v>5</v>
+      </c>
+      <c r="AP19" s="39">
+        <v>4</v>
+      </c>
+      <c r="AQ19" s="39">
+        <v>4</v>
+      </c>
+      <c r="AR19" s="39">
+        <v>3</v>
+      </c>
+      <c r="AS19" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT19" s="39">
+        <v>4</v>
+      </c>
+      <c r="AU19" s="39">
+        <v>3</v>
+      </c>
+      <c r="AV19" s="39">
+        <v>3</v>
+      </c>
+      <c r="AW19" s="39">
+        <v>3</v>
+      </c>
+      <c r="AX19" s="39">
+        <v>2</v>
+      </c>
+      <c r="AY19" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ19" s="39">
+        <v>2</v>
+      </c>
+      <c r="BA19" s="39">
+        <v>4</v>
+      </c>
+      <c r="BB19" s="39">
+        <v>4</v>
+      </c>
+      <c r="BC19" s="39">
+        <v>3</v>
+      </c>
+      <c r="BD19" s="39">
+        <v>3</v>
+      </c>
+      <c r="BE19" s="39">
+        <v>3</v>
+      </c>
+      <c r="BF19" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG19" s="39">
+        <v>3</v>
+      </c>
+      <c r="BH19" s="39">
+        <v>4</v>
+      </c>
+      <c r="BI19" s="39">
+        <v>3</v>
+      </c>
+      <c r="BJ19" s="39">
+        <v>4</v>
+      </c>
+      <c r="BK19" s="39">
+        <v>3</v>
+      </c>
+      <c r="BL19" s="39">
+        <v>3</v>
+      </c>
+      <c r="BM19" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN19" s="39">
+        <v>3</v>
+      </c>
+      <c r="BO19" s="39">
+        <v>4</v>
+      </c>
+      <c r="BP19" s="39">
+        <v>3</v>
+      </c>
+      <c r="BQ19" s="39">
+        <v>4</v>
+      </c>
+      <c r="BR19" s="39">
+        <v>3</v>
+      </c>
+      <c r="BS19" s="39">
+        <v>3</v>
+      </c>
+      <c r="BT19" s="39">
+        <v>5</v>
+      </c>
+      <c r="BU19" s="39">
+        <v>1</v>
+      </c>
+      <c r="BV19" s="39">
+        <v>3</v>
+      </c>
+      <c r="BW19" s="39">
+        <v>3</v>
+      </c>
+      <c r="BX19" s="39">
+        <v>4</v>
+      </c>
+      <c r="BY19" s="39">
+        <v>4</v>
+      </c>
+      <c r="BZ19" s="39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A20" s="40">
+        <v>22</v>
+      </c>
+      <c r="B20" s="39">
+        <v>5</v>
+      </c>
+      <c r="C20" s="39">
+        <v>2</v>
+      </c>
+      <c r="D20" s="39">
+        <v>2</v>
+      </c>
+      <c r="E20" s="39">
+        <v>2</v>
+      </c>
+      <c r="F20" s="39">
+        <v>4</v>
+      </c>
+      <c r="G20" s="39">
+        <v>4</v>
+      </c>
+      <c r="H20" s="39">
+        <v>4</v>
+      </c>
+      <c r="I20" s="39">
+        <v>3</v>
+      </c>
+      <c r="J20" s="39">
+        <v>3</v>
+      </c>
+      <c r="K20" s="39">
+        <v>3</v>
+      </c>
+      <c r="L20" s="39">
+        <v>3</v>
+      </c>
+      <c r="M20" s="39">
+        <v>3</v>
+      </c>
+      <c r="N20" s="39">
+        <v>3</v>
+      </c>
+      <c r="O20" s="39">
+        <v>3</v>
+      </c>
+      <c r="P20" s="39">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="39">
+        <v>4</v>
+      </c>
+      <c r="R20" s="39">
+        <v>3</v>
+      </c>
+      <c r="S20" s="39">
+        <v>3</v>
+      </c>
+      <c r="T20" s="39">
+        <v>4</v>
+      </c>
+      <c r="U20" s="39">
+        <v>4</v>
+      </c>
+      <c r="V20" s="39">
+        <v>4</v>
+      </c>
+      <c r="W20" s="39">
+        <v>3</v>
+      </c>
+      <c r="X20" s="39">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="39">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="39">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="39">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="39">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="39">
+        <v>3</v>
+      </c>
+      <c r="AD20" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE20" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF20" s="39">
+        <v>4</v>
+      </c>
+      <c r="AG20" s="39">
+        <v>4</v>
+      </c>
+      <c r="AH20" s="39">
+        <v>5</v>
+      </c>
+      <c r="AI20" s="39">
+        <v>5</v>
+      </c>
+      <c r="AJ20" s="39">
+        <v>2</v>
+      </c>
+      <c r="AK20" s="39">
+        <v>4</v>
+      </c>
+      <c r="AL20" s="39">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="39">
+        <v>3</v>
+      </c>
+      <c r="AN20" s="39">
+        <v>3</v>
+      </c>
+      <c r="AO20" s="39">
+        <v>5</v>
+      </c>
+      <c r="AP20" s="39">
+        <v>5</v>
+      </c>
+      <c r="AQ20" s="39">
+        <v>2</v>
+      </c>
+      <c r="AR20" s="39">
+        <v>1</v>
+      </c>
+      <c r="AS20" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT20" s="39">
+        <v>3</v>
+      </c>
+      <c r="AU20" s="39">
+        <v>3</v>
+      </c>
+      <c r="AV20" s="39">
+        <v>1</v>
+      </c>
+      <c r="AW20" s="39">
+        <v>1</v>
+      </c>
+      <c r="AX20" s="39">
+        <v>1</v>
+      </c>
+      <c r="AY20" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ20" s="39">
+        <v>4</v>
+      </c>
+      <c r="BA20" s="39">
+        <v>3</v>
+      </c>
+      <c r="BB20" s="39">
+        <v>3</v>
+      </c>
+      <c r="BC20" s="39">
+        <v>4</v>
+      </c>
+      <c r="BD20" s="39">
+        <v>4</v>
+      </c>
+      <c r="BE20" s="39">
+        <v>5</v>
+      </c>
+      <c r="BF20" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG20" s="39">
+        <v>3</v>
+      </c>
+      <c r="BH20" s="39">
+        <v>3</v>
+      </c>
+      <c r="BI20" s="39">
+        <v>3</v>
+      </c>
+      <c r="BJ20" s="39">
+        <v>3</v>
+      </c>
+      <c r="BK20" s="39">
+        <v>3</v>
+      </c>
+      <c r="BL20" s="39">
+        <v>3</v>
+      </c>
+      <c r="BM20" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN20" s="39">
+        <v>3</v>
+      </c>
+      <c r="BO20" s="39">
+        <v>2</v>
+      </c>
+      <c r="BP20" s="39">
+        <v>2</v>
+      </c>
+      <c r="BQ20" s="39">
+        <v>2</v>
+      </c>
+      <c r="BR20" s="39">
+        <v>3</v>
+      </c>
+      <c r="BS20" s="39">
+        <v>3</v>
+      </c>
+      <c r="BT20" s="39">
+        <v>4</v>
+      </c>
+      <c r="BU20" s="39">
+        <v>1</v>
+      </c>
+      <c r="BV20" s="39">
+        <v>2</v>
+      </c>
+      <c r="BW20" s="39">
+        <v>2</v>
+      </c>
+      <c r="BX20" s="39">
+        <v>3</v>
+      </c>
+      <c r="BY20" s="39">
+        <v>3</v>
+      </c>
+      <c r="BZ20" s="39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A21" s="40">
+        <v>23</v>
+      </c>
+      <c r="B21" s="39">
+        <v>5</v>
+      </c>
+      <c r="C21" s="39">
+        <v>2</v>
+      </c>
+      <c r="D21" s="39">
+        <v>3</v>
+      </c>
+      <c r="E21" s="39">
+        <v>3</v>
+      </c>
+      <c r="F21" s="39">
+        <v>3</v>
+      </c>
+      <c r="G21" s="39">
+        <v>4</v>
+      </c>
+      <c r="H21" s="39">
+        <v>4</v>
+      </c>
+      <c r="I21" s="39">
+        <v>4</v>
+      </c>
+      <c r="J21" s="39">
+        <v>4</v>
+      </c>
+      <c r="K21" s="39">
+        <v>4</v>
+      </c>
+      <c r="L21" s="39">
+        <v>4</v>
+      </c>
+      <c r="M21" s="39">
+        <v>4</v>
+      </c>
+      <c r="N21" s="39">
+        <v>4</v>
+      </c>
+      <c r="O21" s="39">
+        <v>4</v>
+      </c>
+      <c r="P21" s="39">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="39">
+        <v>2</v>
+      </c>
+      <c r="R21" s="39">
+        <v>3</v>
+      </c>
+      <c r="S21" s="39">
+        <v>3</v>
+      </c>
+      <c r="T21" s="39">
+        <v>3</v>
+      </c>
+      <c r="U21" s="39">
+        <v>4</v>
+      </c>
+      <c r="V21" s="39">
+        <v>4</v>
+      </c>
+      <c r="W21" s="39">
+        <v>5</v>
+      </c>
+      <c r="X21" s="39">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="39">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AI21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AJ21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AK21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AL21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AM21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AN21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AO21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AP21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AQ21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AR21" s="39">
+        <v>3</v>
+      </c>
+      <c r="AS21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT21" s="39">
+        <v>3</v>
+      </c>
+      <c r="AU21" s="39">
+        <v>3</v>
+      </c>
+      <c r="AV21" s="39">
+        <v>3</v>
+      </c>
+      <c r="AW21" s="39">
+        <v>3</v>
+      </c>
+      <c r="AX21" s="39">
+        <v>3</v>
+      </c>
+      <c r="AY21" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ21" s="39">
+        <v>2</v>
+      </c>
+      <c r="BA21" s="39">
+        <v>3</v>
+      </c>
+      <c r="BB21" s="39">
+        <v>3</v>
+      </c>
+      <c r="BC21" s="39">
+        <v>3</v>
+      </c>
+      <c r="BD21" s="39">
+        <v>4</v>
+      </c>
+      <c r="BE21" s="39">
+        <v>4</v>
+      </c>
+      <c r="BF21" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG21" s="39">
+        <v>2</v>
+      </c>
+      <c r="BH21" s="39">
+        <v>3</v>
+      </c>
+      <c r="BI21" s="39">
+        <v>3</v>
+      </c>
+      <c r="BJ21" s="39">
+        <v>3</v>
+      </c>
+      <c r="BK21" s="39">
+        <v>4</v>
+      </c>
+      <c r="BL21" s="39">
+        <v>4</v>
+      </c>
+      <c r="BM21" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN21" s="39">
+        <v>1</v>
+      </c>
+      <c r="BO21" s="39">
+        <v>1</v>
+      </c>
+      <c r="BP21" s="39">
+        <v>3</v>
+      </c>
+      <c r="BQ21" s="39">
+        <v>3</v>
+      </c>
+      <c r="BR21" s="39">
+        <v>4</v>
+      </c>
+      <c r="BS21" s="39">
+        <v>4</v>
+      </c>
+      <c r="BT21" s="39">
+        <v>5</v>
+      </c>
+      <c r="BU21" s="39">
+        <v>1</v>
+      </c>
+      <c r="BV21" s="39">
+        <v>5</v>
+      </c>
+      <c r="BW21" s="39">
+        <v>5</v>
+      </c>
+      <c r="BX21" s="39">
+        <v>5</v>
+      </c>
+      <c r="BY21" s="39">
+        <v>5</v>
+      </c>
+      <c r="BZ21" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A22" s="40">
+        <v>24</v>
+      </c>
+      <c r="B22" s="39">
+        <v>5</v>
+      </c>
+      <c r="C22" s="39">
+        <v>3</v>
+      </c>
+      <c r="D22" s="39">
+        <v>5</v>
+      </c>
+      <c r="E22" s="39">
+        <v>5</v>
+      </c>
+      <c r="F22" s="39">
+        <v>1</v>
+      </c>
+      <c r="G22" s="39">
+        <v>1</v>
+      </c>
+      <c r="H22" s="39">
+        <v>4</v>
+      </c>
+      <c r="I22" s="39">
+        <v>4</v>
+      </c>
+      <c r="J22" s="39">
+        <v>2</v>
+      </c>
+      <c r="K22" s="39">
+        <v>5</v>
+      </c>
+      <c r="L22" s="39">
+        <v>4</v>
+      </c>
+      <c r="M22" s="39">
+        <v>3</v>
+      </c>
+      <c r="N22" s="39">
+        <v>3</v>
+      </c>
+      <c r="O22" s="39">
+        <v>3</v>
+      </c>
+      <c r="P22" s="39">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="39">
+        <v>2</v>
+      </c>
+      <c r="R22" s="39">
+        <v>5</v>
+      </c>
+      <c r="S22" s="39">
+        <v>5</v>
+      </c>
+      <c r="T22" s="39">
+        <v>3</v>
+      </c>
+      <c r="U22" s="39">
+        <v>3</v>
+      </c>
+      <c r="V22" s="39">
+        <v>3</v>
+      </c>
+      <c r="W22" s="39">
+        <v>4</v>
+      </c>
+      <c r="X22" s="39">
+        <v>2</v>
+      </c>
+      <c r="Y22" s="39">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="39">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="39">
+        <v>3</v>
+      </c>
+      <c r="AB22" s="39">
+        <v>3</v>
+      </c>
+      <c r="AC22" s="39">
+        <v>3</v>
+      </c>
+      <c r="AD22" s="39">
+        <v>4</v>
+      </c>
+      <c r="AE22" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF22" s="39">
+        <v>5</v>
+      </c>
+      <c r="AG22" s="39">
+        <v>4</v>
+      </c>
+      <c r="AH22" s="39">
+        <v>4</v>
+      </c>
+      <c r="AI22" s="39">
+        <v>4</v>
+      </c>
+      <c r="AJ22" s="39">
+        <v>4</v>
+      </c>
+      <c r="AK22" s="39">
+        <v>3</v>
+      </c>
+      <c r="AL22" s="39">
+        <v>4</v>
+      </c>
+      <c r="AM22" s="39">
+        <v>5</v>
+      </c>
+      <c r="AN22" s="39">
+        <v>3</v>
+      </c>
+      <c r="AO22" s="39">
+        <v>3</v>
+      </c>
+      <c r="AP22" s="39">
+        <v>3</v>
+      </c>
+      <c r="AQ22" s="39">
+        <v>3</v>
+      </c>
+      <c r="AR22" s="39">
+        <v>4</v>
+      </c>
+      <c r="AS22" s="39">
+        <v>5</v>
+      </c>
+      <c r="AT22" s="39">
+        <v>4</v>
+      </c>
+      <c r="AU22" s="39">
+        <v>4</v>
+      </c>
+      <c r="AV22" s="39">
+        <v>4</v>
+      </c>
+      <c r="AW22" s="39">
+        <v>4</v>
+      </c>
+      <c r="AX22" s="39">
+        <v>4</v>
+      </c>
+      <c r="AY22" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ22" s="39">
+        <v>1</v>
+      </c>
+      <c r="BA22" s="39">
+        <v>5</v>
+      </c>
+      <c r="BB22" s="39">
+        <v>4</v>
+      </c>
+      <c r="BC22" s="39">
+        <v>2</v>
+      </c>
+      <c r="BD22" s="39">
+        <v>2</v>
+      </c>
+      <c r="BE22" s="39">
+        <v>2</v>
+      </c>
+      <c r="BF22" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG22" s="39">
+        <v>1</v>
+      </c>
+      <c r="BH22" s="39">
+        <v>5</v>
+      </c>
+      <c r="BI22" s="39">
+        <v>3</v>
+      </c>
+      <c r="BJ22" s="39">
+        <v>1</v>
+      </c>
+      <c r="BK22" s="39">
+        <v>1</v>
+      </c>
+      <c r="BL22" s="39">
+        <v>1</v>
+      </c>
+      <c r="BM22" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN22" s="39">
+        <v>1</v>
+      </c>
+      <c r="BO22" s="39">
+        <v>5</v>
+      </c>
+      <c r="BP22" s="39">
+        <v>4</v>
+      </c>
+      <c r="BQ22" s="39">
+        <v>2</v>
+      </c>
+      <c r="BR22" s="39">
+        <v>2</v>
+      </c>
+      <c r="BS22" s="39">
+        <v>2</v>
+      </c>
+      <c r="BT22" s="39">
+        <v>1</v>
+      </c>
+      <c r="BU22" s="39">
+        <v>1</v>
+      </c>
+      <c r="BV22" s="39">
+        <v>5</v>
+      </c>
+      <c r="BW22" s="39">
+        <v>4</v>
+      </c>
+      <c r="BX22" s="39">
+        <v>2</v>
+      </c>
+      <c r="BY22" s="39">
+        <v>2</v>
+      </c>
+      <c r="BZ22" s="39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A23" s="40">
+        <v>25</v>
+      </c>
+      <c r="B23" s="39">
+        <v>5</v>
+      </c>
+      <c r="C23" s="39">
+        <v>1</v>
+      </c>
+      <c r="D23" s="39">
+        <v>4</v>
+      </c>
+      <c r="E23" s="39">
+        <v>2</v>
+      </c>
+      <c r="F23" s="39">
+        <v>5</v>
+      </c>
+      <c r="G23" s="39">
+        <v>5</v>
+      </c>
+      <c r="H23" s="39">
+        <v>5</v>
+      </c>
+      <c r="I23" s="39">
+        <v>4</v>
+      </c>
+      <c r="J23" s="39">
+        <v>1</v>
+      </c>
+      <c r="K23" s="39">
+        <v>4</v>
+      </c>
+      <c r="L23" s="39">
+        <v>5</v>
+      </c>
+      <c r="M23" s="39">
+        <v>4</v>
+      </c>
+      <c r="N23" s="39">
+        <v>4</v>
+      </c>
+      <c r="O23" s="39">
+        <v>4</v>
+      </c>
+      <c r="P23" s="39">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="39">
+        <v>2</v>
+      </c>
+      <c r="R23" s="39">
+        <v>3</v>
+      </c>
+      <c r="S23" s="39">
+        <v>4</v>
+      </c>
+      <c r="T23" s="39">
+        <v>4</v>
+      </c>
+      <c r="U23" s="39">
+        <v>4</v>
+      </c>
+      <c r="V23" s="39">
+        <v>5</v>
+      </c>
+      <c r="W23" s="39">
+        <v>3</v>
+      </c>
+      <c r="X23" s="39">
+        <v>5</v>
+      </c>
+      <c r="Y23" s="39">
+        <v>4</v>
+      </c>
+      <c r="Z23" s="39">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="39">
+        <v>3</v>
+      </c>
+      <c r="AB23" s="39">
+        <v>3</v>
+      </c>
+      <c r="AC23" s="39">
+        <v>1</v>
+      </c>
+      <c r="AD23" s="39">
+        <v>5</v>
+      </c>
+      <c r="AE23" s="39">
+        <v>5</v>
+      </c>
+      <c r="AF23" s="39">
+        <v>4</v>
+      </c>
+      <c r="AG23" s="39">
+        <v>1</v>
+      </c>
+      <c r="AH23" s="39">
+        <v>5</v>
+      </c>
+      <c r="AI23" s="39">
+        <v>5</v>
+      </c>
+      <c r="AJ23" s="39">
+        <v>5</v>
+      </c>
+      <c r="AK23" s="39">
+        <v>2</v>
+      </c>
+      <c r="AL23" s="39">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="39">
+        <v>2</v>
+      </c>
+      <c r="AN23" s="39">
+        <v>3</v>
+      </c>
+      <c r="AO23" s="39">
+        <v>2</v>
+      </c>
+      <c r="AP23" s="39">
+        <v>4</v>
+      </c>
+      <c r="AQ23" s="39">
+        <v>2</v>
+      </c>
+      <c r="AR23" s="39">
+        <v>3</v>
+      </c>
+      <c r="AS23" s="39">
+        <v>4</v>
+      </c>
+      <c r="AT23" s="39">
+        <v>3</v>
+      </c>
+      <c r="AU23" s="39">
+        <v>3</v>
+      </c>
+      <c r="AV23" s="39">
+        <v>3</v>
+      </c>
+      <c r="AW23" s="39">
+        <v>3</v>
+      </c>
+      <c r="AX23" s="39">
+        <v>3</v>
+      </c>
+      <c r="AY23" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ23" s="39">
+        <v>1</v>
+      </c>
+      <c r="BA23" s="39">
+        <v>3</v>
+      </c>
+      <c r="BB23" s="39">
+        <v>5</v>
+      </c>
+      <c r="BC23" s="39">
+        <v>3</v>
+      </c>
+      <c r="BD23" s="39">
+        <v>4</v>
+      </c>
+      <c r="BE23" s="39">
+        <v>4</v>
+      </c>
+      <c r="BF23" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG23" s="39">
+        <v>1</v>
+      </c>
+      <c r="BH23" s="39">
+        <v>4</v>
+      </c>
+      <c r="BI23" s="39">
+        <v>4</v>
+      </c>
+      <c r="BJ23" s="39">
+        <v>4</v>
+      </c>
+      <c r="BK23" s="39">
+        <v>4</v>
+      </c>
+      <c r="BL23" s="39">
+        <v>4</v>
+      </c>
+      <c r="BM23" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN23" s="39">
+        <v>1</v>
+      </c>
+      <c r="BO23" s="39">
+        <v>3</v>
+      </c>
+      <c r="BP23" s="39">
+        <v>3</v>
+      </c>
+      <c r="BQ23" s="39">
+        <v>4</v>
+      </c>
+      <c r="BR23" s="39">
+        <v>4</v>
+      </c>
+      <c r="BS23" s="39">
+        <v>5</v>
+      </c>
+      <c r="BT23" s="39">
+        <v>5</v>
+      </c>
+      <c r="BU23" s="39">
+        <v>1</v>
+      </c>
+      <c r="BV23" s="39">
+        <v>4</v>
+      </c>
+      <c r="BW23" s="39">
+        <v>4</v>
+      </c>
+      <c r="BX23" s="39">
+        <v>4</v>
+      </c>
+      <c r="BY23" s="39">
+        <v>5</v>
+      </c>
+      <c r="BZ23" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A24" s="40">
+        <v>26</v>
+      </c>
+      <c r="B24" s="39">
+        <v>4</v>
+      </c>
+      <c r="C24" s="39">
+        <v>3</v>
+      </c>
+      <c r="D24" s="39">
+        <v>2</v>
+      </c>
+      <c r="E24" s="39">
+        <v>2</v>
+      </c>
+      <c r="F24" s="39">
+        <v>2</v>
+      </c>
+      <c r="G24" s="39">
+        <v>2</v>
+      </c>
+      <c r="H24" s="39">
+        <v>3</v>
+      </c>
+      <c r="I24" s="39">
+        <v>4</v>
+      </c>
+      <c r="J24" s="39">
+        <v>3</v>
+      </c>
+      <c r="K24" s="39">
+        <v>2</v>
+      </c>
+      <c r="L24" s="39">
+        <v>2</v>
+      </c>
+      <c r="M24" s="39">
+        <v>2</v>
+      </c>
+      <c r="N24" s="39">
+        <v>2</v>
+      </c>
+      <c r="O24" s="39">
+        <v>2</v>
+      </c>
+      <c r="P24" s="39">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="39">
+        <v>4</v>
+      </c>
+      <c r="R24" s="39">
+        <v>3</v>
+      </c>
+      <c r="S24" s="39">
+        <v>3</v>
+      </c>
+      <c r="T24" s="39">
+        <v>3</v>
+      </c>
+      <c r="U24" s="39">
+        <v>3</v>
+      </c>
+      <c r="V24" s="39">
+        <v>4</v>
+      </c>
+      <c r="W24" s="39">
+        <v>4</v>
+      </c>
+      <c r="X24" s="39">
+        <v>4</v>
+      </c>
+      <c r="Y24" s="39">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="39">
+        <v>3</v>
+      </c>
+      <c r="AA24" s="39">
+        <v>3</v>
+      </c>
+      <c r="AB24" s="39">
+        <v>3</v>
+      </c>
+      <c r="AC24" s="39">
+        <v>3</v>
+      </c>
+      <c r="AD24" s="39">
+        <v>4</v>
+      </c>
+      <c r="AE24" s="39">
+        <v>4</v>
+      </c>
+      <c r="AF24" s="39">
+        <v>2</v>
+      </c>
+      <c r="AG24" s="39">
+        <v>2</v>
+      </c>
+      <c r="AH24" s="39">
+        <v>2</v>
+      </c>
+      <c r="AI24" s="39">
+        <v>2</v>
+      </c>
+      <c r="AJ24" s="39">
+        <v>2</v>
+      </c>
+      <c r="AK24" s="39">
+        <v>4</v>
+      </c>
+      <c r="AL24" s="39">
+        <v>4</v>
+      </c>
+      <c r="AM24" s="39">
+        <v>3</v>
+      </c>
+      <c r="AN24" s="39">
+        <v>2</v>
+      </c>
+      <c r="AO24" s="39">
+        <v>2</v>
+      </c>
+      <c r="AP24" s="39">
+        <v>2</v>
+      </c>
+      <c r="AQ24" s="39">
+        <v>3</v>
+      </c>
+      <c r="AR24" s="39">
+        <v>4</v>
+      </c>
+      <c r="AS24" s="39">
+        <v>1</v>
+      </c>
+      <c r="AT24" s="39">
+        <v>3</v>
+      </c>
+      <c r="AU24" s="39">
+        <v>3</v>
+      </c>
+      <c r="AV24" s="39">
+        <v>3</v>
+      </c>
+      <c r="AW24" s="39">
+        <v>3</v>
+      </c>
+      <c r="AX24" s="39">
+        <v>3</v>
+      </c>
+      <c r="AY24" s="39">
+        <v>4</v>
+      </c>
+      <c r="AZ24" s="39">
+        <v>2</v>
+      </c>
+      <c r="BA24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BB24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BC24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BD24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BE24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BF24" s="39">
+        <v>4</v>
+      </c>
+      <c r="BG24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BH24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BI24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BJ24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BK24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BL24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BM24" s="39">
+        <v>4</v>
+      </c>
+      <c r="BN24" s="39">
+        <v>2</v>
+      </c>
+      <c r="BO24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BP24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BQ24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BR24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BS24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BT24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BU24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BV24" s="39">
+        <v>4</v>
+      </c>
+      <c r="BW24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BX24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BY24" s="39">
+        <v>3</v>
+      </c>
+      <c r="BZ24" s="39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A25" s="40">
+        <v>27</v>
+      </c>
+      <c r="B25" s="39">
+        <v>5</v>
+      </c>
+      <c r="C25" s="39">
+        <v>1</v>
+      </c>
+      <c r="D25" s="39">
+        <v>1</v>
+      </c>
+      <c r="E25" s="39">
+        <v>1</v>
+      </c>
+      <c r="F25" s="39">
+        <v>1</v>
+      </c>
+      <c r="G25" s="39">
+        <v>1</v>
+      </c>
+      <c r="H25" s="39">
+        <v>1</v>
+      </c>
+      <c r="I25" s="39">
+        <v>5</v>
+      </c>
+      <c r="J25" s="39">
+        <v>1</v>
+      </c>
+      <c r="K25" s="39">
+        <v>1</v>
+      </c>
+      <c r="L25" s="39">
+        <v>1</v>
+      </c>
+      <c r="M25" s="39">
+        <v>1</v>
+      </c>
+      <c r="N25" s="39">
+        <v>1</v>
+      </c>
+      <c r="O25" s="39">
+        <v>1</v>
+      </c>
+      <c r="P25" s="39">
+        <v>5</v>
+      </c>
+      <c r="Q25" s="39">
+        <v>1</v>
+      </c>
+      <c r="R25" s="39">
+        <v>1</v>
+      </c>
+      <c r="S25" s="39">
+        <v>1</v>
+      </c>
+      <c r="T25" s="39">
+        <v>1</v>
+      </c>
+      <c r="U25" s="39">
+        <v>1</v>
+      </c>
+      <c r="V25" s="39">
+        <v>1</v>
+      </c>
+      <c r="W25" s="39">
+        <v>5</v>
+      </c>
+      <c r="X25" s="39">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="39">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="39">
+        <v>3</v>
+      </c>
+      <c r="AE25" s="39">
+        <v>3</v>
+      </c>
+      <c r="AF25" s="39">
+        <v>3</v>
+      </c>
+      <c r="AG25" s="39">
+        <v>3</v>
+      </c>
+      <c r="AH25" s="39">
+        <v>3</v>
+      </c>
+      <c r="AI25" s="39">
+        <v>3</v>
+      </c>
+      <c r="AJ25" s="39">
+        <v>3</v>
+      </c>
+      <c r="AK25" s="39">
+        <v>5</v>
+      </c>
+      <c r="AL25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AM25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AN25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AO25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AP25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AQ25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AR25" s="39">
+        <v>5</v>
+      </c>
+      <c r="AS25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AT25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AU25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AV25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AW25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AX25" s="39">
+        <v>1</v>
+      </c>
+      <c r="AY25" s="39">
+        <v>5</v>
+      </c>
+      <c r="AZ25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BA25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BB25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BC25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BD25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BE25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BF25" s="39">
+        <v>5</v>
+      </c>
+      <c r="BG25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BH25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BI25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BJ25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BK25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BL25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BM25" s="39">
+        <v>5</v>
+      </c>
+      <c r="BN25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BO25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BP25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BQ25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BR25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BS25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BT25" s="39">
+        <v>4</v>
+      </c>
+      <c r="BU25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BV25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BW25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BX25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BY25" s="39">
+        <v>1</v>
+      </c>
+      <c r="BZ25" s="39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A26" s="40">
+        <v>28</v>
+      </c>
+      <c r="B26" s="39">
+        <v>3</v>
+      </c>
+      <c r="C26" s="39">
+        <v>2</v>
+      </c>
+      <c r="D26" s="39">
+        <v>1</v>
+      </c>
+      <c r="E26" s="39">
+        <v>1</v>
+      </c>
+      <c r="F26" s="39">
+        <v>3</v>
+      </c>
+      <c r="G26" s="39">
+        <v>3</v>
+      </c>
+      <c r="H26" s="39">
+        <v>2</v>
+      </c>
+      <c r="I26" s="39">
+        <v>4</v>
+      </c>
+      <c r="J26" s="39">
+        <v>4</v>
+      </c>
+      <c r="K26" s="39">
+        <v>4</v>
+      </c>
+      <c r="L26" s="39">
+        <v>4</v>
+      </c>
+      <c r="M26" s="39">
+        <v>4</v>
+      </c>
+      <c r="N26" s="39">
+        <v>4</v>
+      </c>
+      <c r="O26" s="39">
+        <v>4</v>
+      </c>
+      <c r="P26" s="39">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="39">
+        <v>1</v>
+      </c>
+      <c r="R26" s="39">
+        <v>1</v>
+      </c>
+      <c r="S26" s="39">
+        <v>1</v>
+      </c>
+      <c r="T26" s="39">
+        <v>3</v>
+      </c>
+      <c r="U26" s="39">
+        <v>3</v>
+      </c>
+      <c r="V26" s="39">
+        <v>3</v>
+      </c>
+      <c r="W26" s="39">
+        <v>2</v>
+      </c>
+      <c r="X26" s="39">
+        <v>4</v>
+      </c>
+      <c r="Y26" s="39">
+        <v>4</v>
+      </c>
+      <c r="Z26" s="39">
+        <v>4</v>
+      </c>
+      <c r="AA26" s="39">
+        <v>2</v>
+      </c>
+      <c r="AB26" s="39">
+        <v>3</v>
+      </c>
+      <c r="AC26" s="39">
+        <v>3</v>
+      </c>
+      <c r="AD26" s="39">
+        <v>4</v>
+      </c>
+      <c r="AE26" s="39">
+        <v>4</v>
+      </c>
+      <c r="AF26" s="39">
+        <v>2</v>
+      </c>
+      <c r="AG26" s="39">
+        <v>2</v>
+      </c>
+      <c r="AH26" s="39">
+        <v>4</v>
+      </c>
+      <c r="AI26" s="39">
+        <v>4</v>
+      </c>
+      <c r="AJ26" s="39">
+        <v>4</v>
+      </c>
+      <c r="AK26" s="39">
+        <v>4</v>
+      </c>
+      <c r="AL26" s="39">
+        <v>4</v>
+      </c>
+      <c r="AM26" s="39">
+        <v>4</v>
+      </c>
+      <c r="AN26" s="39">
+        <v>4</v>
+      </c>
+      <c r="AO26" s="39">
+        <v>4</v>
+      </c>
+      <c r="AP26" s="39">
+        <v>4</v>
+      </c>
+      <c r="AQ26" s="39">
+        <v>4</v>
+      </c>
+      <c r="AR26" s="39">
+        <v>2</v>
+      </c>
+      <c r="AS26" s="39">
+        <v>4</v>
+      </c>
+      <c r="AT26" s="39">
+        <v>2</v>
+      </c>
+      <c r="AU26" s="39">
+        <v>1</v>
+      </c>
+      <c r="AV26" s="39">
+        <v>2</v>
+      </c>
+      <c r="AW26" s="39">
+        <v>2</v>
+      </c>
+      <c r="AX26" s="39">
+        <v>2</v>
+      </c>
+      <c r="AY26" s="39">
+        <v>4</v>
+      </c>
+      <c r="AZ26" s="39">
+        <v>2</v>
+      </c>
+      <c r="BA26" s="39">
+        <v>1</v>
+      </c>
+      <c r="BB26" s="39">
+        <v>3</v>
+      </c>
+      <c r="BC26" s="39">
+        <v>3</v>
+      </c>
+      <c r="BD26" s="39">
+        <v>3</v>
+      </c>
+      <c r="BE26" s="39">
+        <v>3</v>
+      </c>
+      <c r="BF26" s="39">
+        <v>4</v>
+      </c>
+      <c r="BG26" s="39">
+        <v>2</v>
+      </c>
+      <c r="BH26" s="39">
+        <v>1</v>
+      </c>
+      <c r="BI26" s="39">
+        <v>2</v>
+      </c>
+      <c r="BJ26" s="39">
+        <v>3</v>
+      </c>
+      <c r="BK26" s="39">
+        <v>3</v>
+      </c>
+      <c r="BL26" s="39">
+        <v>3</v>
+      </c>
+      <c r="BM26" s="39">
+        <v>4</v>
+      </c>
+      <c r="BN26" s="39">
+        <v>1</v>
+      </c>
+      <c r="BO26" s="39">
+        <v>1</v>
+      </c>
+      <c r="BP26" s="39">
+        <v>1</v>
+      </c>
+      <c r="BQ26" s="39">
+        <v>2</v>
+      </c>
+      <c r="BR26" s="39">
+        <v>2</v>
+      </c>
+      <c r="BS26" s="39">
+        <v>2</v>
+      </c>
+      <c r="BT26" s="39">
+        <v>4</v>
+      </c>
+      <c r="BU26" s="39">
+        <v>3</v>
+      </c>
+      <c r="BV26" s="39">
+        <v>1</v>
+      </c>
+      <c r="BW26" s="39">
+        <v>3</v>
+      </c>
+      <c r="BX26" s="39">
+        <v>4</v>
+      </c>
+      <c r="BY26" s="39">
+        <v>4</v>
+      </c>
+      <c r="BZ26" s="39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:78" x14ac:dyDescent="0.15">
+      <c r="A27" s="40">
+        <v>30</v>
+      </c>
+      <c r="B27" s="39">
+        <v>3</v>
+      </c>
+      <c r="C27" s="39">
+        <v>2</v>
+      </c>
+      <c r="D27" s="39">
+        <v>4</v>
+      </c>
+      <c r="E27" s="39">
+        <v>4</v>
+      </c>
+      <c r="F27" s="39">
+        <v>4</v>
+      </c>
+      <c r="G27" s="39">
+        <v>4</v>
+      </c>
+      <c r="H27" s="39">
+        <v>4</v>
+      </c>
+      <c r="I27" s="39">
+        <v>2</v>
+      </c>
+      <c r="J27" s="39">
+        <v>1</v>
+      </c>
+      <c r="K27" s="39">
+        <v>4</v>
+      </c>
+      <c r="L27" s="39">
+        <v>4</v>
+      </c>
+      <c r="M27" s="39">
+        <v>4</v>
+      </c>
+      <c r="N27" s="39">
+        <v>4</v>
+      </c>
+      <c r="O27" s="39">
+        <v>4</v>
+      </c>
+      <c r="P27" s="39">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="39">
+        <v>3</v>
+      </c>
+      <c r="R27" s="39">
+        <v>3</v>
+      </c>
+      <c r="S27" s="39">
+        <v>3</v>
+      </c>
+      <c r="T27" s="39">
+        <v>3</v>
+      </c>
+      <c r="U27" s="39">
+        <v>3</v>
+      </c>
+      <c r="V27" s="39">
+        <v>3</v>
+      </c>
+      <c r="W27" s="39">
+        <v>3</v>
+      </c>
+      <c r="X27" s="39">
+        <v>2</v>
+      </c>
+      <c r="Y27" s="39">
+        <v>4</v>
+      </c>
+      <c r="Z27" s="39">
+        <v>4</v>
+      </c>
+      <c r="AA27" s="39">
+        <v>2</v>
+      </c>
+      <c r="AB27" s="39">
+        <v>2</v>
+      </c>
+      <c r="AC27" s="39">
+        <v>2</v>
+      </c>
+      <c r="AD27" s="39">
+        <v>3</v>
+      </c>
+      <c r="AE27" s="39">
+        <v>3</v>
+      </c>
+      <c r="AF27" s="39">
+        <v>3</v>
+      </c>
+      <c r="AG27" s="39">
+        <v>3</v>
+      </c>
+      <c r="AH27" s="39">
+        <v>3</v>
+      </c>
+      <c r="AI27" s="39">
+        <v>3</v>
+      </c>
+      <c r="AJ27" s="39">
+        <v>3</v>
+      </c>
+      <c r="AK27" s="39">
+        <v>3</v>
+      </c>
+      <c r="AL27" s="39">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="39">
+        <v>3</v>
+      </c>
+      <c r="AN27" s="39">
+        <v>3</v>
+      </c>
+      <c r="AO27" s="39">
+        <v>3</v>
+      </c>
+      <c r="AP27" s="39">
+        <v>3</v>
+      </c>
+      <c r="AQ27" s="39">
+        <v>3</v>
+      </c>
+      <c r="AR27" s="39">
+        <v>2</v>
+      </c>
+      <c r="AS27" s="39">
+        <v>4</v>
+      </c>
+      <c r="AT27" s="39">
+        <v>2</v>
+      </c>
+      <c r="AU27" s="39">
+        <v>2</v>
+      </c>
+      <c r="AV27" s="39">
+        <v>2</v>
+      </c>
+      <c r="AW27" s="39">
+        <v>2</v>
+      </c>
+      <c r="AX27" s="39">
+        <v>2</v>
+      </c>
+      <c r="AY27" s="39">
+        <v>3</v>
+      </c>
+      <c r="AZ27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BA27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BB27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BC27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BD27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BE27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BF27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BG27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BH27" s="39">
+        <v>4</v>
+      </c>
+      <c r="BI27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BJ27" s="39">
+        <v>2</v>
+      </c>
+      <c r="BK27" s="39">
+        <v>2</v>
+      </c>
+      <c r="BL27" s="39">
+        <v>2</v>
+      </c>
+      <c r="BM27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BN27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BO27" s="39">
+        <v>4</v>
+      </c>
+      <c r="BP27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BQ27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BR27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BS27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BT27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BU27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BV27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BW27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BX27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BY27" s="39">
+        <v>3</v>
+      </c>
+      <c r="BZ27" s="39">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A3DDE04-695C-704A-BF07-36F460538C0E}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="30" style="22" customWidth="1"/>
+    <col min="2" max="4" width="16" style="22" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="38" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="36">
+        <v>0.8203945313026989</v>
+      </c>
+      <c r="C2" s="35">
+        <v>0.25750590497021941</v>
+      </c>
+      <c r="D2" s="35">
+        <v>0.22878061522771109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" s="35">
+        <v>0.3569869178630149</v>
+      </c>
+      <c r="C3" s="36">
+        <v>0.81528655346040624</v>
+      </c>
+      <c r="D3" s="35">
+        <v>6.7056223701106296E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="36">
+        <v>0.75446678915921994</v>
+      </c>
+      <c r="C4" s="35">
+        <v>0.3512326710793216</v>
+      </c>
+      <c r="D4" s="35">
+        <v>0.169226766406642</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5" s="35">
+        <v>1.7600480029897302E-2</v>
+      </c>
+      <c r="C5" s="36">
+        <v>0.93770086381307383</v>
+      </c>
+      <c r="D5" s="35">
+        <v>0.10167370293994921</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" s="33">
+        <v>0.29566119469411473</v>
+      </c>
+      <c r="C6" s="33">
+        <v>-0.23534689451466359</v>
+      </c>
+      <c r="D6" s="32">
+        <v>0.77663869302358424</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" s="33">
+        <v>0.35498913706479379</v>
+      </c>
+      <c r="C7" s="33">
+        <v>0.28924227357125232</v>
+      </c>
+      <c r="D7" s="32">
+        <v>0.56610668751947268</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="33">
+        <v>-3.10140078183073E-2</v>
+      </c>
+      <c r="C8" s="33">
+        <v>0.24783079953736259</v>
+      </c>
+      <c r="D8" s="32">
+        <v>0.7667701241873035</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" s="30">
+        <v>0.90199212335881684</v>
+      </c>
+      <c r="C9" s="29">
+        <v>0.2258458990504055</v>
+      </c>
+      <c r="D9" s="29">
+        <v>6.9167090489873004E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="30">
+        <v>0.92970689906531356</v>
+      </c>
+      <c r="C10" s="29">
+        <v>-6.8918562723874997E-3</v>
+      </c>
+      <c r="D10" s="29">
+        <v>0.1492369167479316</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="30">
+        <v>0.90256788809233157</v>
+      </c>
+      <c r="C11" s="29">
+        <v>-9.8902919560373101E-2</v>
+      </c>
+      <c r="D11" s="29">
+        <v>0.23139609567408001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="30">
+        <v>0.55332528684791649</v>
+      </c>
+      <c r="C12" s="29">
+        <v>0.30863463113119688</v>
+      </c>
+      <c r="D12" s="29">
+        <v>-0.36064891721164849</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A13" s="28"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A14" s="27"/>
+      <c r="B14" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>